--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1177,781 +1177,781 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>TbDishBase</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>DishBase</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>dish_base.xlsx</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>dish_base@dish.xlsx</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>菜品本体：不随标签变化的物理属性（id/name/deliciousness/icon/allowRotate/shapeRows）。</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>TbDishVariant</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>DishVariant</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>dish_variant.xlsx</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>dish_variant@dish.xlsx</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>菜品变体：随机菜品库条目。引用本体+标签组合+隐藏分/权重/价格。同 baseId 不同变体=带不同标签视为不同菜品。aTagId/bTagId 空串=唯一标签槽为空。</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>TbTag</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>tag.xlsx</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>标签（技能）。category 区分固有/唯一A/唯一B；termId 非空时菜品详情额外展示该名词。</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>TbTerm</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>term.xlsx</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>专有名词：菜品详情右侧框单独解释。</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>TbCharacter</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Character</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>character.xlsx</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>角色：initialFragmentId 指向初始胃形状(碎片库)；maxStomachWidth/Height 为胃最大包围盒。</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>TbStomachFragment</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>StomachFragment</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>stomach_fragment.xlsx</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>胃部碎片库：也用作初始胃形状来源。碎片不旋转(1x2 与 2x1 视为两个碎片)。'X'=存在格。</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>TbFragmentCellTag</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>FragmentCellTag</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>fragment_cell_tag.xlsx</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>碎片格强化标签：一行=碎片某格(x,y)挂一个标签 id（引用 TbTag）。</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>TbRecipe</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Recipe</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>recipe.xlsx</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>菜谱：固定菜品+加权放回随机池(pool: list,RecipeEntry)，随机到累计初始分&gt;=requiredInitScore 为止。</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>TbItem</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>item.xlsx</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>道具：被动常驻/主动可触发。specialTags 用 | 分隔，空串=无。acquireLimit/holdLimit&lt;=0 无限制；consumeOnUse 仅主动道具生效。</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>TbScoreProfile</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>ScoreProfile</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>score_profile.xlsx</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>目标分曲线：周/关卡引用它生成本局要求分，无尽模式沿用最后一周曲线增长。</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>TbRewardPackage</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>RewardPackage</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>reward_package.xlsx</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>reward_package@reward.xlsx</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>胜利奖励包：固定金币+主奖励槽组+可选额外奖励槽组。</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>TbRewardSlot</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>RewardSlot</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>reward_slot.xlsx</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>reward_slot@reward.xlsx</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>奖励槽：同 groupId 内按 weight 选一个槽，再按槽规则生成候选。</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>TbRewardPool</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>RewardPool</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>reward_pool.xlsx</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>reward_pool@reward.xlsx</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>奖励池筛选：qualityWeights 写 Common:70|Uncommon:25|Rare:5；specialTags 用 | 分隔。</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>TbWeek</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>week.xlsx</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>周/关卡：目标分、奖励包和隐藏分随进度推进；isBoss 为特殊天。</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>TbEvent</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>GameEvent</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>event.xlsx</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>event@event.xlsx</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>事件：行动/节点触发的局外事件。effectType/effectValue 为无选项快捷事件直接结算；若 TbEventOption 有该 eventId 选项则改弹选项。repeatable=false 命中后写入 UsedEventIds。</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>TbEventOption</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>EventOption</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>event_option.xlsx</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>event_option@event.xlsx</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>事件选项：同 eventId 多行=该事件可选项。resultType/resultValue/resultParam 由 EventService 分发结算。</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>TbAction</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>GameAction</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>action.xlsx</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>行动（三选一）：行动轴每步从满足条件的行动按权重随机3个。actionType 决定执行分支；costDays 推进天数；repeatable=false 命中后写入 UsedActionIds；linkId：Event→TbEvent，Food→TbScoreProfile。</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>TbTimeline</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Timeline</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>timeline.xlsx</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>timeline@timeline.xlsx</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>行动轴库：按周筛选(weekFilter:空=任意/normal/boss/逗号分隔周号)后按 weight 随机一条。baseLengthDays 为轴长度。</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>TbTimelineNode</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>TimelineNode</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>timeline_node.xlsx</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>timeline_node@timeline.xlsx</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>行动轴节点：同 timelineId 多行=该轴节点。day 为整天位置(1..baseLengthDays)。interest:payloadValue=利息阈值N,payloadParam=每阈值金币数;shop:无;boss:payloadParam=Boss池筛选;event:payloadParam=指定事件id。</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>TbBoss</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>boss.xlsx</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Boss：Boss节点按权重随机。characterPool 空=任意角色；week=0 任意周；unlockCondition 空=默认解锁；scoreProfileId 空=用当前周曲线；modifier 为特殊机制(limit_serve/small_board…)。</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>TbGlobalConst</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>GlobalConst</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>globalconst.xlsx</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>GlobalConst：跑通 Luban 接入用的占位表（与玩法无关）。</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1503,7 +1503,7 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>道具：被动常驻/主动可触发。specialTags 用 | 分隔，空串=无。acquireLimit/holdLimit&lt;=0 无限制；consumeOnUse 仅主动道具生效。</t>
+          <t>道具：被动常驻/主动可触发。specialTags 用 | 分隔，空串=无。holdLimit&lt;=0 表示主动道具无持有上限。</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col width="29.1047619047619" customWidth="1" style="3" min="2" max="2"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>action.xlsx</t>
+          <t>action@action.xlsx</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1952,6 +1952,166 @@
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>TbActionGroup</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>ActionGroup</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>action_group@action.xlsx</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>行动组：一段可展示的行动组合。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>TbActionGroupMember</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ActionGroupMember</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>action_group_member@action.xlsx</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>行动组成员：组内行动、耗时随机范围与权重。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>TbActionScheduleRule</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ActionScheduleRule</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>action_schedule_rule@action.xlsx</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>行动日程规则：区间/窗口约束和优先级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>TbHiddenScoreCurve</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>HiddenScoreCurve</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>hidden_score_curve@reward_curve.xlsx</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>隐藏分曲线：基础隐藏分与派生隐藏分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>TbGoldRewardCurve</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>GoldRewardCurve</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>gold_reward_curve@reward_curve.xlsx</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>金币奖励曲线：按进度和行动难度计算上下限。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1528,7 +1528,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>score_profile.xlsx</t>
+          <t>score_profile@timeline.xlsx</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>目标分曲线：周/关卡引用它生成本局要求分，无尽模式沿用最后一周曲线增长。</t>
+          <t>目标分曲线：与 week 同在 timeline.xlsx；Week.scoreProfileId/Boss.scoreProfileId 引用它生成普通与 Boss 目标分。</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>reward_package@reward.xlsx</t>
+          <t>reward_package@timeline.xlsx</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>胜利奖励包：固定金币+主奖励槽组+可选额外奖励槽组。</t>
+          <t>奖励包：与 week 同在 timeline.xlsx；Week.rewardPackageId/Action.rewardPackageId 引用它，槽组继续指向 reward.xlsx/reward_slot。</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>week.xlsx</t>
+          <t>week@timeline.xlsx</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>周/关卡：目标分、奖励包和隐藏分随进度推进；isBoss 为特殊天。</t>
+          <t>周/关卡配置：定义每周的目标分曲线、默认奖励包、奖励隐藏分与 Boss 周标记；与行动轴表同在 timeline.xlsx，进入新周时先读 Week 再按 isBoss 筛选 Timeline。</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>行动轴库：按周筛选(weekFilter:空=任意/normal/boss/逗号分隔周号)后按 weight 随机一条。baseLengthDays 为轴长度。</t>
+          <t>行动轴库：按当前 Week 的 isBoss 与 weekFilter（空=任意/normal/boss/逗号周号）筛选后按 weight 随机；baseLengthDays 为轴基础长度。</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1873,7 +1873,7 @@
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>行动轴节点：同 timelineId 多行=该轴节点。day 为整天位置(1..baseLengthDays)。interest:payloadValue=利息阈值N,payloadParam=每阈值金币数;shop:无;boss:payloadParam=Boss池筛选;event:payloadParam=指定事件id。</t>
+          <t>行动轴节点：同 timelineId 多行组成一条轴；行动推进时触发 prevDay &lt; day &lt;= newDay 且未触发过的节点，并按 day 升序结算。</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col width="29.1047619047619" customWidth="1" style="3" min="2" max="2"/>
@@ -1355,7 +1355,7 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>角色：initialFragmentId 指向初始胃形状(碎片库)；maxStomachWidth/Height 为胃最大包围盒。</t>
+          <t>角色：配置初始菜谱/胃形状/道具，并通过 timelinePool/bossPool 限制该角色可随机到的行动轴和 Boss。</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1725,7 +1725,7 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>事件：行动/节点触发的局外事件。effectType/effectValue 为无选项快捷事件直接结算；若 TbEventOption 有该 eventId 选项则改弹选项。repeatable=false 命中后写入 UsedEventIds。</t>
+          <t>事件：行动/节点触发的局外事件。weight 用于事件节点随机；repeatable=false 命中后写入 UsedEventIds。</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1956,12 +1956,12 @@
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TbActionGroup</t>
+          <t>TbHiddenScoreCurve</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ActionGroup</t>
+          <t>HiddenScoreCurve</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>action_group@action.xlsx</t>
+          <t>hidden_score_curve@reward_curve.xlsx</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1981,19 +1981,19 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>行动组：一段可展示的行动组合。</t>
+          <t>隐藏分曲线：基础隐藏分与派生隐藏分。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TbActionGroupMember</t>
+          <t>TbGoldRewardCurve</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ActionGroupMember</t>
+          <t>GoldRewardCurve</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>action_group_member@action.xlsx</t>
+          <t>gold_reward_curve@reward_curve.xlsx</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2012,102 +2012,6 @@
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>行动组成员：组内行动、耗时随机范围与权重。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>TbActionScheduleRule</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>ActionScheduleRule</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>action_schedule_rule@action.xlsx</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>行动日程规则：区间/窗口约束和优先级。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>TbHiddenScoreCurve</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>HiddenScoreCurve</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>hidden_score_curve@reward_curve.xlsx</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>隐藏分曲线：基础隐藏分与派生隐藏分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>TbGoldRewardCurve</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>GoldRewardCurve</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>gold_reward_curve@reward_curve.xlsx</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>金币奖励曲线：按进度和行动难度计算上下限。</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col width="29.1047619047619" customWidth="1" style="3" min="2" max="2"/>
@@ -1795,11 +1795,11 @@
           <t>id</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>行动（三选一）：行动轴每步从满足条件的行动按权重随机3个。actionType 决定执行分支；costDays 推进天数；repeatable=false 命中后写入 UsedActionIds；linkId：Event→TbEvent，Food→TbScoreProfile。</t>
+          <t>行动（三选一）：由行动组成员筛选后进入候选。actionType 决定执行分支；costDays 为默认耗时。</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -2014,6 +2014,102 @@
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>金币奖励曲线：按进度和行动难度计算上下限。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>TbActionGroup</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>ActionGroup</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>action_group@action.xlsx</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>行动组：控制整局行动组合序列的奖励外观、难度和节奏。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>TbActionGroupMember</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>ActionGroupMember</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>action_group_member@action.xlsx</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>行动组成员：指定组内候选行动、组内权重和本次耗时范围。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>TbActionScheduleRule</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>ActionScheduleRule</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>action_schedule_rule@action.xlsx</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>整局行动日程规则：按整局行动序号窗口和优先级填充行动组序列。</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col width="29.1047619047619" customWidth="1" style="3" min="2" max="2"/>
@@ -2113,6 +2113,70 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TbUnlockRule</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>UnlockRule</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>unlock_rule@unlock.xlsx</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>解锁规则：一条规则定义一个跨局可解锁目标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TbUnlockCondition</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>UnlockCondition</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>unlock_condition@unlock.xlsx</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1466,7 +1466,7 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>菜谱：固定菜品+加权放回随机池(pool: list,RecipeEntry)，随机到累计初始分&gt;=requiredInitScore 为止。</t>
+          <t>菜谱：固定菜品(fixedDishes 用 | 分隔)+加权放回随机池(pool: list,RecipeEntry)，随机到累计初始分&gt;=requiredInitScore 为止。</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -2114,64 +2114,64 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>TbUnlockRule</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UnlockRule</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>unlock_rule@unlock.xlsx</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>解锁规则：一条规则定义一个跨局可解锁目标。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>TbUnlockCondition</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UnlockCondition</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>unlock_condition@unlock.xlsx</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col width="29.1047619047619" customWidth="1" style="3" min="2" max="2"/>
@@ -1244,7 +1244,7 @@
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>菜品变体：随机菜品库条目。引用本体+标签组合+隐藏分/权重/价格。同 baseId 不同变体=带不同标签视为不同菜品。aTagId/bTagId 空串=唯一标签槽为空。</t>
+          <t>菜品变体：随机菜品库条目。引用本体+技能(skills→TbSkill)+风味(flavorId→TbFlavor,单槽)+隐藏分/权重/价格。同 baseId 不同组合视为不同菜品。flavorId 空串=无风味。</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -1254,12 +1254,12 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TbTag</t>
+          <t>TbTerm</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Term</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>tag.xlsx</t>
+          <t>term.xlsx</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1281,7 +1281,7 @@
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>标签（技能）。category 区分固有/唯一A/唯一B；termId 非空时菜品详情额外展示该名词。</t>
+          <t>专有名词：菜品详情右侧框单独解释。</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -1291,12 +1291,12 @@
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TbTerm</t>
+          <t>TbCharacter</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Term</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>term.xlsx</t>
+          <t>character.xlsx</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>专有名词：菜品详情右侧框单独解释。</t>
+          <t>角色：配置初始菜谱/胃形状/道具，并通过 timelinePool/bossPool 限制该角色可随机到的行动轴和 Boss。</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -1328,12 +1328,12 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>TbCharacter</t>
+          <t>TbStomachFragment</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>StomachFragment</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>character.xlsx</t>
+          <t>stomach_fragment.xlsx</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>角色：配置初始菜谱/胃形状/道具，并通过 timelinePool/bossPool 限制该角色可随机到的行动轴和 Boss。</t>
+          <t>胃部碎片库：也用作初始胃形状来源。碎片不旋转(1x2 与 2x1 视为两个碎片)。'X'=存在格。</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1365,12 +1365,12 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TbStomachFragment</t>
+          <t>TbFragmentCellTag</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>StomachFragment</t>
+          <t>FragmentCellTag</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>stomach_fragment.xlsx</t>
+          <t>fragment_cell_tag.xlsx</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>胃部碎片库：也用作初始胃形状来源。碎片不旋转(1x2 与 2x1 视为两个碎片)。'X'=存在格。</t>
+          <t>碎片格强化标签：一行=碎片某格(x,y)挂一个格子标签 id（引用 TbCellTag）。</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -1402,12 +1402,12 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>TbFragmentCellTag</t>
+          <t>TbRecipe</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>FragmentCellTag</t>
+          <t>Recipe</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>fragment_cell_tag.xlsx</t>
+          <t>recipe.xlsx</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>碎片格强化标签：一行=碎片某格(x,y)挂一个标签 id（引用 TbTag）。</t>
+          <t>菜谱：固定菜品(fixedDishes 用 | 分隔)+加权放回随机池(pool: list,RecipeEntry)，随机到累计初始分&gt;=requiredInitScore 为止。</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1439,12 +1439,12 @@
       <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>TbRecipe</t>
+          <t>TbItem</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>recipe.xlsx</t>
+          <t>item.xlsx</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1466,7 +1466,7 @@
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>菜谱：固定菜品(fixedDishes 用 | 分隔)+加权放回随机池(pool: list,RecipeEntry)，随机到累计初始分&gt;=requiredInitScore 为止。</t>
+          <t>道具：被动常驻/主动可触发。specialTags 用 | 分隔，空串=无。holdLimit&lt;=0 表示主动道具无持有上限。</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1476,12 +1476,12 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>TbItem</t>
+          <t>TbScoreProfile</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>ScoreProfile</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>item.xlsx</t>
+          <t>score_profile@timeline.xlsx</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>道具：被动常驻/主动可触发。specialTags 用 | 分隔，空串=无。holdLimit&lt;=0 表示主动道具无持有上限。</t>
+          <t>目标分曲线：与 week 同在 timeline.xlsx；Week.scoreProfileId/Boss.scoreProfileId 引用它生成普通与 Boss 目标分。</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1513,12 +1513,12 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>TbScoreProfile</t>
+          <t>TbRewardPackage</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ScoreProfile</t>
+          <t>RewardPackage</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>score_profile@timeline.xlsx</t>
+          <t>reward_package@timeline.xlsx</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>目标分曲线：与 week 同在 timeline.xlsx；Week.scoreProfileId/Boss.scoreProfileId 引用它生成普通与 Boss 目标分。</t>
+          <t>奖励包：与 week 同在 timeline.xlsx；Week.rewardPackageId/Action.rewardPackageId 引用它，槽组继续指向 reward.xlsx/reward_slot。</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1550,12 +1550,12 @@
       <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>TbRewardPackage</t>
+          <t>TbRewardSlot</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>RewardPackage</t>
+          <t>RewardSlot</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>reward_package@timeline.xlsx</t>
+          <t>reward_slot@reward.xlsx</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>奖励包：与 week 同在 timeline.xlsx；Week.rewardPackageId/Action.rewardPackageId 引用它，槽组继续指向 reward.xlsx/reward_slot。</t>
+          <t>奖励槽：同 groupId 内按 weight 选一个槽，再按槽规则生成候选。</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1587,12 +1587,12 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>TbRewardSlot</t>
+          <t>TbRewardPool</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>RewardSlot</t>
+          <t>RewardPool</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>reward_slot@reward.xlsx</t>
+          <t>reward_pool@reward.xlsx</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>奖励槽：同 groupId 内按 weight 选一个槽，再按槽规则生成候选。</t>
+          <t>奖励池筛选：qualityWeights 写 Common:70|Uncommon:25|Rare:5；specialTags 用 | 分隔。</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1624,12 +1624,12 @@
       <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>TbRewardPool</t>
+          <t>TbWeek</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>RewardPool</t>
+          <t>Week</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>reward_pool@reward.xlsx</t>
+          <t>week@timeline.xlsx</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>奖励池筛选：qualityWeights 写 Common:70|Uncommon:25|Rare:5；specialTags 用 | 分隔。</t>
+          <t>周/关卡配置：定义每周的目标分曲线、默认奖励包、奖励隐藏分与 Boss 周标记；与行动轴表同在 timeline.xlsx，进入新周时先读 Week 再按 isBoss 筛选 Timeline。</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1661,12 +1661,12 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>TbWeek</t>
+          <t>TbEvent</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>GameEvent</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>week@timeline.xlsx</t>
+          <t>event@event.xlsx</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>周/关卡配置：定义每周的目标分曲线、默认奖励包、奖励隐藏分与 Boss 周标记；与行动轴表同在 timeline.xlsx，进入新周时先读 Week 再按 isBoss 筛选 Timeline。</t>
+          <t>事件：行动/节点触发的局外事件。weight 用于事件节点随机；repeatable=false 命中后写入 UsedEventIds。</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1698,12 +1698,12 @@
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>TbEvent</t>
+          <t>TbEventOption</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>GameEvent</t>
+          <t>EventOption</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>event@event.xlsx</t>
+          <t>event_option@event.xlsx</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>事件：行动/节点触发的局外事件。weight 用于事件节点随机；repeatable=false 命中后写入 UsedEventIds。</t>
+          <t>事件选项：同 eventId 多行=该事件可选项。resultType/resultValue/resultParam 由 EventService 分发结算。</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1735,12 +1735,12 @@
       <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>TbEventOption</t>
+          <t>TbAction</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EventOption</t>
+          <t>GameAction</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>event_option@event.xlsx</t>
+          <t>action@action.xlsx</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1758,11 +1758,11 @@
           <t>id</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>事件选项：同 eventId 多行=该事件可选项。resultType/resultValue/resultParam 由 EventService 分发结算。</t>
+          <t>行动（三选一）：由行动组成员筛选后进入候选。actionType 决定执行分支；costDays 为默认耗时。</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1772,12 +1772,12 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>TbAction</t>
+          <t>TbTimeline</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>GameAction</t>
+          <t>Timeline</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>action@action.xlsx</t>
+          <t>timeline@timeline.xlsx</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1795,11 +1795,11 @@
           <t>id</t>
         </is>
       </c>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>行动（三选一）：由行动组成员筛选后进入候选。actionType 决定执行分支；costDays 为默认耗时。</t>
+          <t>行动轴库：按当前 Week 的 isBoss 与 weekFilter（空=任意/normal/boss/逗号周号）筛选后按 weight 随机；baseLengthDays 为轴基础长度。</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1809,12 +1809,12 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>TbTimeline</t>
+          <t>TbTimelineNode</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Timeline</t>
+          <t>TimelineNode</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>timeline@timeline.xlsx</t>
+          <t>timeline_node@timeline.xlsx</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>行动轴库：按当前 Week 的 isBoss 与 weekFilter（空=任意/normal/boss/逗号周号）筛选后按 weight 随机；baseLengthDays 为轴基础长度。</t>
+          <t>行动轴节点：同 timelineId 多行组成一条轴；行动推进时触发 prevDay &lt; day &lt;= newDay 且未触发过的节点，并按 day 升序结算。</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1846,12 +1846,12 @@
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>TbTimelineNode</t>
+          <t>TbBoss</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>TimelineNode</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>timeline_node@timeline.xlsx</t>
+          <t>boss.xlsx</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1873,7 +1873,7 @@
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>行动轴节点：同 timelineId 多行组成一条轴；行动推进时触发 prevDay &lt; day &lt;= newDay 且未触发过的节点，并按 day 升序结算。</t>
+          <t>Boss：Boss节点按权重随机。characterPool 空=任意角色；week=0 任意周；unlockCondition 空=默认解锁；scoreProfileId 空=用当前周曲线；modifier 为特殊机制(limit_serve/small_board…)。</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1883,12 +1883,12 @@
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>TbBoss</t>
+          <t>TbGlobalConst</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>GlobalConst</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>boss.xlsx</t>
+          <t>globalconst.xlsx</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1910,22 +1910,21 @@
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Boss：Boss节点按权重随机。characterPool 空=任意角色；week=0 任意周；unlockCondition 空=默认解锁；scoreProfileId 空=用当前周曲线；modifier 为特殊机制(limit_serve/small_board…)。</t>
+          <t>GlobalConst：跑通 Luban 接入用的占位表（与玩法无关）。</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TbGlobalConst</t>
+          <t>TbHiddenScoreCurve</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>GlobalConst</t>
+          <t>HiddenScoreCurve</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1935,7 +1934,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>globalconst.xlsx</t>
+          <t>hidden_score_curve@reward_curve.xlsx</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1943,25 +1942,21 @@
           <t>id</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>GlobalConst：跑通 Luban 接入用的占位表（与玩法无关）。</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
+          <t>隐藏分曲线：基础隐藏分与派生隐藏分。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TbHiddenScoreCurve</t>
+          <t>TbGoldRewardCurve</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>HiddenScoreCurve</t>
+          <t>GoldRewardCurve</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1971,7 +1966,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>hidden_score_curve@reward_curve.xlsx</t>
+          <t>gold_reward_curve@reward_curve.xlsx</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1981,19 +1976,19 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>隐藏分曲线：基础隐藏分与派生隐藏分。</t>
+          <t>金币奖励曲线：按进度和行动难度计算上下限。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TbGoldRewardCurve</t>
+          <t>TbActionGroup</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>GoldRewardCurve</t>
+          <t>ActionGroup</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2003,7 +1998,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>gold_reward_curve@reward_curve.xlsx</t>
+          <t>action_group@action.xlsx</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2013,19 +2008,19 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>金币奖励曲线：按进度和行动难度计算上下限。</t>
+          <t>行动组：控制整局行动组合序列的奖励外观、难度和节奏。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>TbActionGroup</t>
+          <t>TbActionGroupMember</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ActionGroup</t>
+          <t>ActionGroupMember</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2035,7 +2030,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>action_group@action.xlsx</t>
+          <t>action_group_member@action.xlsx</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2045,19 +2040,19 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>行动组：控制整局行动组合序列的奖励外观、难度和节奏。</t>
+          <t>行动组成员：指定组内候选行动、组内权重和本次耗时范围。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>TbActionGroupMember</t>
+          <t>TbActionScheduleRule</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ActionGroupMember</t>
+          <t>ActionScheduleRule</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2067,7 +2062,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>action_group_member@action.xlsx</t>
+          <t>action_schedule_rule@action.xlsx</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2077,19 +2072,19 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>行动组成员：指定组内候选行动、组内权重和本次耗时范围。</t>
+          <t>整局行动日程规则：按整局行动序号窗口和优先级填充行动组序列。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>TbActionScheduleRule</t>
+          <t>TbUnlockRule</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ActionScheduleRule</t>
+          <t>UnlockRule</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2099,7 +2094,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>action_schedule_rule@action.xlsx</t>
+          <t>unlock_rule@unlock.xlsx</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2109,19 +2104,19 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>整局行动日程规则：按整局行动序号窗口和优先级填充行动组序列。</t>
+          <t>解锁规则：一条规则定义一个跨局可解锁目标。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>TbUnlockRule</t>
+          <t>TbUnlockCondition</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>UnlockRule</t>
+          <t>UnlockCondition</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2131,7 +2126,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>unlock_rule@unlock.xlsx</t>
+          <t>unlock_condition@unlock.xlsx</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2141,39 +2136,103 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>解锁规则：一条规则定义一个跨局可解锁目标。</t>
+          <t>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>TbUnlockCondition</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>UnlockCondition</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>unlock_condition@unlock.xlsx</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</t>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TbSkill</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>skill.xlsx</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>菜品技能：数量无上限。effectType/effectValue 定义结算效果；termId 非空时详情额外展示名词。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TbFlavor</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Flavor</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>flavor.xlsx</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>菜品风味：单槽，后者替换前者。effectType/effectValue 定义结算效果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TbCellTag</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CellTag</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>cell_tag.xlsx</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>棋盘格子标签：挂在胃碎片格上（TbFragmentCellTag 引用）。effectType/effectValue 定义结算效果。</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1380,7 +1380,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>fragment_cell_tag.xlsx</t>
+          <t>fragment_cell_tag@fragment_cell_tag.xlsx</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2141,96 +2141,96 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>TbSkill</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Skill</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>skill.xlsx</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>skill@dish.xlsx</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>菜品技能：数量无上限。effectType/effectValue 定义结算效果；termId 非空时详情额外展示名词。</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>TbFlavor</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Flavor</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>flavor.xlsx</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>flavor@dish.xlsx</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>菜品风味：单槽，后者替换前者。effectType/effectValue 定义结算效果。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>TbCellTag</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>CellTag</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>cell_tag.xlsx</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>cell_tag@fragment_cell_tag.xlsx</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>棋盘格子标签：挂在胃碎片格上（TbFragmentCellTag 引用）。effectType/effectValue 定义结算效果。</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col width="29.1047619047619" customWidth="1" style="3" min="2" max="2"/>
@@ -2236,6 +2236,38 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TbSkillRule</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SkillRule</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>skill_rule@dish.xlsx</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>菜品技能规则：一行=一条规则(前提×行为)，同skillId多行按order执行。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1207,7 +1207,7 @@
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>菜品本体：不随标签变化的物理属性（id/name/deliciousness/icon/allowRotate/shapeRows）。</t>
+          <t>菜品本体：物理属性（id/name/deliciousness/icon/allowRotate/shapeRows）与固有技能（skills→TbSkill）。</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -1244,7 +1244,7 @@
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>菜品变体：随机菜品库条目。引用本体+技能(skills→TbSkill)+风味(flavorId→TbFlavor,单槽)+隐藏分/权重/价格。同 baseId 不同组合视为不同菜品。flavorId 空串=无风味。</t>
+          <t>菜品变体：随机菜品库条目。引用本体+风味(flavorId→TbFlavor,单槽)+隐藏分/权重/价格。flavorId 空串=无风味。</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>菜品技能：数量无上限。effectType/effectValue 定义结算效果；termId 非空时详情额外展示名词。</t>
+          <t>菜品技能元信息：id/name/desc/termId。具体效果统一由 TbSkillRule 配置。</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>菜品风味：单槽，后者替换前者。effectType/effectValue 定义结算效果。</t>
+          <t>菜品风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</t>
         </is>
       </c>
     </row>
@@ -2237,34 +2237,34 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>TbSkillRule</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>SkillRule</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>skill_rule@dish.xlsx</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>菜品技能规则：一行=一条规则(前提×行为)，同skillId多行按order执行。</t>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>菜品技能规则：一行=一条规则(前提×行为)，同skillId多行按order执行。所有菜品技能效果统一走本表。</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5"/>
   <cols>
     <col width="29.1047619047619" customWidth="1" style="3" min="2" max="2"/>
@@ -2268,6 +2268,38 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TbCakeLayerBuff</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CakeLayerBuff</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>cake_layer_buff@dish.xlsx</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -2168,7 +2168,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>菜品技能元信息：id/name/desc/termId。具体效果统一由 TbSkillRule 配置。</t>
+          <t>菜品技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</t>
         </is>
       </c>
     </row>
@@ -2239,12 +2239,12 @@
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>TbSkillRule</t>
+          <t>TbCakeLayerBuff</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>SkillRule</t>
+          <t>CakeLayerBuff</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>skill_rule@dish.xlsx</t>
+          <t>cake_layer_buff@dish.xlsx</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2264,39 +2264,39 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>菜品技能规则：一行=一条规则(前提×行为)，同skillId多行按order执行。所有菜品技能效果统一走本表。</t>
+          <t>欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>TbCakeLayerBuff</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CakeLayerBuff</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>cake_layer_buff@dish.xlsx</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</t>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>TbSubSkill</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>SubSkill</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>sub_skill@dish.xlsx</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + isPassive/signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2060,12 +2060,12 @@
     <row r="32">
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>TbEvent</t>
+          <t>TbBossDebuff</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>GameEvent</t>
+          <t>BossDebuff</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>event@event.xlsx</t>
+          <t>boss_debuff@food.xlsx</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
@@ -2085,19 +2085,19 @@
       </c>
       <c r="I32" s="0" t="inlineStr">
         <is>
-          <t>事件明细：eventType 分类(Event/Reward/Negative)，公共 preconditions/weight/repeatable。</t>
+          <t>Boss 盛宴 Debuff：Boss 美食战斗独立抽取，不放回随机；抽空后重置历史。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>TbEventOption</t>
+          <t>TbEvent</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>EventOption</t>
+          <t>GameEvent</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>event_option@event.xlsx</t>
+          <t>event@event.xlsx</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
@@ -2117,19 +2117,19 @@
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t>事件选项：同 eventId 多行=选项分支；单选项=自动结算。effectType 用 EffectType。</t>
+          <t>事件明细：eventType 分类(Event/Reward/Negative)，公共 preconditions/weight/repeatable。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>TbActionSmallGroup</t>
+          <t>TbEventOption</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>ActionSmallGroup</t>
+          <t>EventOption</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>small_group@action.xlsx</t>
+          <t>event_option@event.xlsx</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
@@ -2149,19 +2149,19 @@
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t>小组：固定成员（成员见 small_member），即本次 n 选一。</t>
+          <t>事件选项：同 eventId 多行=选项分支；单选项=自动结算。effectType 用 EffectType。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>TbActionSmallMember</t>
+          <t>TbActionSmallGroup</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>ActionSmallMember</t>
+          <t>ActionSmallGroup</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>small_member@action.xlsx</t>
+          <t>small_group@action.xlsx</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
@@ -2181,19 +2181,19 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>小组成员：小组内固定行动。</t>
+          <t>小组：固定成员（成员见 small_member），即本次 n 选一。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>TbActionMediumGroup</t>
+          <t>TbActionSmallMember</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>ActionMediumGroup</t>
+          <t>ActionSmallMember</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>medium_group@action.xlsx</t>
+          <t>small_member@action.xlsx</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
@@ -2213,19 +2213,19 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>中组：含多个小组(见 medium_member)，被大组按 weight 选中。</t>
+          <t>小组成员：小组内固定行动。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>TbActionMediumMember</t>
+          <t>TbActionMediumGroup</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>ActionMediumMember</t>
+          <t>ActionMediumGroup</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>medium_member@action.xlsx</t>
+          <t>medium_group@action.xlsx</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
@@ -2245,19 +2245,19 @@
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t>中组成员：中组内按 weight 选一个小组。</t>
+          <t>中组：含多个小组(见 medium_member)，被大组按 weight 选中。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>TbActionLargeGroup</t>
+          <t>TbActionMediumMember</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>ActionLargeGroup</t>
+          <t>ActionMediumMember</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>large_group@action.xlsx</t>
+          <t>medium_member@action.xlsx</t>
         </is>
       </c>
       <c r="F38" s="0" t="inlineStr">
@@ -2277,19 +2277,19 @@
       </c>
       <c r="I38" s="0" t="inlineStr">
         <is>
-          <t>大组：含多个中组(见 large_member)；ruleIds 参与日程规则，fallbackWeights 保底随机。</t>
+          <t>中组成员：中组内按 weight 选一个小组。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>TbActionLargeMember</t>
+          <t>TbActionLargeGroup</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>ActionLargeMember</t>
+          <t>ActionLargeGroup</t>
         </is>
       </c>
       <c r="D39" s="0" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>large_member@action.xlsx</t>
+          <t>large_group@action.xlsx</t>
         </is>
       </c>
       <c r="F39" s="0" t="inlineStr">
@@ -2309,38 +2309,70 @@
       </c>
       <c r="I39" s="0" t="inlineStr">
         <is>
-          <t>大组成员：大组内按 中组.weight 选一个中组。</t>
+          <t>大组：含多个中组(见 large_member)；ruleIds 参与日程规则，fallbackWeights 保底随机。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="0" t="inlineStr">
         <is>
+          <t>TbActionLargeMember</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>ActionLargeMember</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>large_member@action.xlsx</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I40" s="0" t="inlineStr">
+        <is>
+          <t>大组成员：大组内按 中组.weight 选一个中组。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="0" t="inlineStr">
+        <is>
           <t>TbGameBase</t>
         </is>
       </c>
-      <c r="C40" s="0" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>GameBase</t>
         </is>
       </c>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E40" s="0" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>game_base.xlsx</t>
         </is>
       </c>
-      <c r="F40" s="0" t="n"/>
-      <c r="G40" t="inlineStr">
+      <c r="F41" s="0" t="n"/>
+      <c r="G41" s="0" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="I40" s="0" t="inlineStr">
+      <c r="I41" s="0" t="inlineStr">
         <is>
           <t>全局基础配置：整局初始金币、利息与食物调整等基础数值。</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1573,7 +1573,7 @@
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>周/关卡配置：定义每周的目标分曲线、默认奖励包、奖励隐藏分与 Boss 周标记；与行动轴表同在 timeline.xlsx，进入新周时先读 Week 再按 isBoss 筛选 Timeline。</t>
+          <t>周/关卡配置：定义每周的目标分曲线、默认奖励包、奖励隐藏分、候选行动轴列表与行动轴权重。</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t>行动轴库：按当前 Week 的 isBoss 与 weekFilter（空=任意/normal/boss/逗号周号）筛选后按 weight 随机；baseLengthDays 为轴基础长度。</t>
+          <t>行动轴库：定义行动轴模板与基础长度；具体每周候选池和权重由 Week.timelineIds/timelineWeights 决定。</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>美食/战斗明细（含 Boss）：Food 行动 foodId 关联；Boss=isBoss，按角色池/周/解锁随机。</t>
+          <t>美食/战斗明细（含 Boss）：Food 行动 foodId 关联；Boss=isBoss，按角色池/解锁条件随机。</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
       </c>
       <c r="I39" s="0" t="inlineStr">
         <is>
-          <t>大组：含多个中组(见 large_member)；ruleIds 参与日程规则，fallbackWeights 保底随机。</t>
+          <t>行动大组：按保底权重、日程规则与前置条件参与随机，不做周筛选。</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2181,19 +2181,19 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>小组：固定成员（成员见 small_member），即本次 n 选一。</t>
+          <t>小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>TbActionSmallMember</t>
+          <t>TbActionMediumGroup</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>ActionSmallMember</t>
+          <t>ActionMediumGroup</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>small_member@action.xlsx</t>
+          <t>medium_group@action.xlsx</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
@@ -2213,19 +2213,19 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>小组成员：小组内固定行动。</t>
+          <t>中组：内嵌 smallGroupEntries(list,ActionSmallGroupEntry) 按权重选一个小组；中组自身 weight 供大组挑选。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>TbActionMediumGroup</t>
+          <t>TbActionLargeGroup</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>ActionMediumGroup</t>
+          <t>ActionLargeGroup</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>medium_group@action.xlsx</t>
+          <t>large_group@action.xlsx</t>
         </is>
       </c>
       <c r="F37" s="0" t="inlineStr">
@@ -2245,19 +2245,19 @@
       </c>
       <c r="I37" s="0" t="inlineStr">
         <is>
-          <t>中组：含多个小组(见 medium_member)，被大组按 weight 选中。</t>
+          <t>行动大组：内嵌 mediumGroupIds(list,string)，按保底权重与日程规则参与随机。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>TbActionMediumMember</t>
+          <t>TbGameBase</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>ActionMediumMember</t>
+          <t>GameBase</t>
         </is>
       </c>
       <c r="D38" s="0" t="inlineStr">
@@ -2267,112 +2267,16 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>medium_member@action.xlsx</t>
-        </is>
-      </c>
-      <c r="F38" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
+          <t>game_base.xlsx</t>
+        </is>
+      </c>
+      <c r="F38" s="0" t="n"/>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>one</t>
         </is>
       </c>
       <c r="I38" s="0" t="inlineStr">
-        <is>
-          <t>中组成员：中组内按 weight 选一个小组。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="0" t="inlineStr">
-        <is>
-          <t>TbActionLargeGroup</t>
-        </is>
-      </c>
-      <c r="C39" s="0" t="inlineStr">
-        <is>
-          <t>ActionLargeGroup</t>
-        </is>
-      </c>
-      <c r="D39" s="0" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E39" s="0" t="inlineStr">
-        <is>
-          <t>large_group@action.xlsx</t>
-        </is>
-      </c>
-      <c r="F39" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I39" s="0" t="inlineStr">
-        <is>
-          <t>行动大组：按保底权重、日程规则与前置条件参与随机，不做周筛选。</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="0" t="inlineStr">
-        <is>
-          <t>TbActionLargeMember</t>
-        </is>
-      </c>
-      <c r="C40" s="0" t="inlineStr">
-        <is>
-          <t>ActionLargeMember</t>
-        </is>
-      </c>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E40" s="0" t="inlineStr">
-        <is>
-          <t>large_member@action.xlsx</t>
-        </is>
-      </c>
-      <c r="F40" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="I40" s="0" t="inlineStr">
-        <is>
-          <t>大组成员：大组内按 中组.weight 选一个中组。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t>TbGameBase</t>
-        </is>
-      </c>
-      <c r="C41" s="0" t="inlineStr">
-        <is>
-          <t>GameBase</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t>game_base.xlsx</t>
-        </is>
-      </c>
-      <c r="F41" s="0" t="n"/>
-      <c r="G41" s="0" t="inlineStr">
-        <is>
-          <t>one</t>
-        </is>
-      </c>
-      <c r="I41" s="0" t="inlineStr">
         <is>
           <t>全局基础配置：整局初始金币、利息与食物调整等基础数值。</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2181,19 +2181,19 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选。</t>
+          <t>小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选；weight 供大组挑选。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>TbActionMediumGroup</t>
+          <t>TbActionLargeGroup</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>ActionMediumGroup</t>
+          <t>ActionLargeGroup</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>medium_group@action.xlsx</t>
+          <t>large_group@action.xlsx</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
@@ -2213,19 +2213,19 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>中组：内嵌 smallGroupEntries(list,ActionSmallGroupEntry) 按权重选一个小组；中组自身 weight 供大组挑选。</t>
+          <t>行动大组：内嵌 smallGroupIds(list,string)，按保底权重与日程规则参与随机。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>TbActionLargeGroup</t>
+          <t>TbGameBase</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>ActionLargeGroup</t>
+          <t>GameBase</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
@@ -2235,48 +2235,16 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>large_group@action.xlsx</t>
-        </is>
-      </c>
-      <c r="F37" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
+          <t>game_base.xlsx</t>
+        </is>
+      </c>
+      <c r="F37" s="0" t="n"/>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>one</t>
         </is>
       </c>
       <c r="I37" s="0" t="inlineStr">
-        <is>
-          <t>行动大组：内嵌 mediumGroupIds(list,string)，按保底权重与日程规则参与随机。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="0" t="inlineStr">
-        <is>
-          <t>TbGameBase</t>
-        </is>
-      </c>
-      <c r="C38" s="0" t="inlineStr">
-        <is>
-          <t>GameBase</t>
-        </is>
-      </c>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E38" s="0" t="inlineStr">
-        <is>
-          <t>game_base.xlsx</t>
-        </is>
-      </c>
-      <c r="F38" s="0" t="n"/>
-      <c r="G38" s="0" t="inlineStr">
-        <is>
-          <t>one</t>
-        </is>
-      </c>
-      <c r="I38" s="0" t="inlineStr">
         <is>
           <t>全局基础配置：整局初始金币、利息与食物调整等基础数值。</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1292,12 +1292,12 @@
     <row r="8">
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>TbStomachFragment</t>
+          <t>TbTableFragment</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>StomachFragment</t>
+          <t>TableFragment</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="E8" s="0" t="inlineStr">
         <is>
-          <t>stomach_fragment.xlsx</t>
+          <t>table_fragment.xlsx</t>
         </is>
       </c>
       <c r="F8" s="0" t="inlineStr">
@@ -1324,12 +1324,12 @@
     <row r="9">
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>TbFragmentCellTag</t>
+          <t>TbFragmentMaterial</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>FragmentCellTag</t>
+          <t>FragmentMaterial</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>fragment_cell_tag@fragment_cell_tag.xlsx</t>
+          <t>fragment_material@fragment_material.xlsx</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
@@ -1932,12 +1932,12 @@
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>TbCellTag</t>
+          <t>TbMaterial</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>CellTag</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>cell_tag@fragment_cell_tag.xlsx</t>
+          <t>material@fragment_material.xlsx</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1349,7 +1349,7 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t>碎片格强化标签：一行=碎片某格(x,y)挂一个格子标签 id（引用 TbCellTag）。</t>
+          <t>碎片格材质：一行=碎片某格(x,y)挂一个材质 id（引用 TbMaterial）。</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t>棋盘格子标签：挂在胃碎片格上（TbFragmentCellTag 引用）。effectType/effectValue 定义结算效果。</t>
+          <t>餐桌材质：挂在餐桌碎片格上（TbFragmentMaterial 引用）。effectType/effectValue 定义结算效果。</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,12 +1388,12 @@
     <row r="11">
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>TbItem</t>
+          <t>TbPassiveItem</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>PassiveItem</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>item.xlsx</t>
+          <t>被动道具@item.xlsx</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
@@ -1413,19 +1413,19 @@
       </c>
       <c r="I11" s="0" t="inlineStr">
         <is>
-          <t>道具：被动常驻/主动可触发。specialTags 用 | 分隔，空串=无。</t>
+          <t>被动道具：永久常驻/获得时生效，道具池按隐藏分筛选。specialTags 用 | 分隔，空串=无。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>TbScoreProfile</t>
+          <t>TbActiveItem</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>ScoreProfile</t>
+          <t>ActiveItem</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>score_profile@timeline.xlsx</t>
+          <t>主动道具@item.xlsx</t>
         </is>
       </c>
       <c r="F12" s="0" t="inlineStr">
@@ -1445,19 +1445,19 @@
       </c>
       <c r="I12" s="0" t="inlineStr">
         <is>
-          <t>目标分曲线：与 week 同在 timeline.xlsx；Week.scoreProfileId/Boss.scoreProfileId 引用它生成普通与 Boss 目标分。</t>
+          <t>主动道具：一次性占全局消耗槽，玩家手动使用；不配置隐藏分区间。specialTags 用 | 分隔，空串=无。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>TbRewardPackage</t>
+          <t>TbScoreProfile</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>RewardPackage</t>
+          <t>ScoreProfile</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>reward_package@timeline.xlsx</t>
+          <t>score_profile@timeline.xlsx</t>
         </is>
       </c>
       <c r="F13" s="0" t="inlineStr">
@@ -1477,19 +1477,19 @@
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t>奖励包：与 week 同在 timeline.xlsx；Week.rewardPackageId/Action.rewardPackageId 引用它，槽组继续指向 reward.xlsx/reward_slot。</t>
+          <t>目标分曲线：与 week 同在 timeline.xlsx；Week.scoreProfileId/Boss.scoreProfileId 引用它生成普通与 Boss 目标分。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>TbRewardSlot</t>
+          <t>TbRewardPackage</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>RewardSlot</t>
+          <t>RewardPackage</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>reward_slot@reward.xlsx</t>
+          <t>reward_package@timeline.xlsx</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
@@ -1509,19 +1509,19 @@
       </c>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t>奖励槽：同 groupId 内按 weight 选一个槽，再按槽规则生成候选。</t>
+          <t>奖励包：与 week 同在 timeline.xlsx；Week.rewardPackageId/Action.rewardPackageId 引用它，槽组继续指向 reward.xlsx/reward_slot。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>TbRewardPool</t>
+          <t>TbRewardSlot</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>RewardPool</t>
+          <t>RewardSlot</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t>reward_pool@reward.xlsx</t>
+          <t>reward_slot@reward.xlsx</t>
         </is>
       </c>
       <c r="F15" s="0" t="inlineStr">
@@ -1541,19 +1541,19 @@
       </c>
       <c r="I15" s="0" t="inlineStr">
         <is>
-          <t>奖励池筛选：qualityWeights 写 Common:70|Uncommon:25|Rare:5；specialTags 用 | 分隔。</t>
+          <t>奖励槽：同 groupId 内按 weight 选一个槽，再按槽规则生成候选。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>TbWeek</t>
+          <t>TbRewardPool</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>Week</t>
+          <t>RewardPool</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>week@timeline.xlsx</t>
+          <t>reward_pool@reward.xlsx</t>
         </is>
       </c>
       <c r="F16" s="0" t="inlineStr">
@@ -1573,19 +1573,19 @@
       </c>
       <c r="I16" s="0" t="inlineStr">
         <is>
-          <t>周/关卡配置：定义每周的目标分曲线、默认奖励包、奖励隐藏分、候选行动轴列表与行动轴权重。</t>
+          <t>奖励池筛选：qualityWeights 写 Common:70|Uncommon:25|Rare:5；specialTags 用 | 分隔。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>TbAction</t>
+          <t>TbWeek</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>GameAction</t>
+          <t>Week</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>action@action.xlsx</t>
+          <t>week@timeline.xlsx</t>
         </is>
       </c>
       <c r="F17" s="0" t="inlineStr">
@@ -1605,19 +1605,19 @@
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t>行动（薄壳分派）：只留 behavior 与关联/少量参数；具体内容在 TbFood/TbEvent。</t>
+          <t>周/关卡配置：定义每周的目标分曲线、默认奖励包、奖励隐藏分、候选行动轴列表与行动轴权重。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>TbTimeline</t>
+          <t>TbAction</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>Timeline</t>
+          <t>GameAction</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>timeline@timeline.xlsx</t>
+          <t>action@action.xlsx</t>
         </is>
       </c>
       <c r="F18" s="0" t="inlineStr">
@@ -1637,19 +1637,19 @@
       </c>
       <c r="I18" s="0" t="inlineStr">
         <is>
-          <t>行动轴库：定义行动轴模板与基础长度；具体每周候选池和权重由 Week.timelineIds/timelineWeights 决定。</t>
+          <t>行动（薄壳分派）：只留 behavior 与关联/少量参数；具体内容在 TbFood/TbEvent。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>TbTimelineNode</t>
+          <t>TbTimeline</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>TimelineNode</t>
+          <t>Timeline</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>timeline_node@timeline.xlsx</t>
+          <t>timeline@timeline.xlsx</t>
         </is>
       </c>
       <c r="F19" s="0" t="inlineStr">
@@ -1669,19 +1669,19 @@
       </c>
       <c r="I19" s="0" t="inlineStr">
         <is>
-          <t>行动轴节点：同 timelineId 多行组成一条轴；行动推进时触发 prevDay &lt; day &lt;= newDay 且未触发过的节点，并按 day 升序结算。</t>
+          <t>行动轴库：定义行动轴模板与基础长度；具体每周候选池和权重由 Week.timelineIds/timelineWeights 决定。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>TbGlobalConst</t>
+          <t>TbTimelineNode</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>GlobalConst</t>
+          <t>TimelineNode</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>globalconst.xlsx</t>
+          <t>timeline_node@timeline.xlsx</t>
         </is>
       </c>
       <c r="F20" s="0" t="inlineStr">
@@ -1701,19 +1701,19 @@
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t>GlobalConst：跑通 Luban 接入用的占位表（与玩法无关）。</t>
+          <t>行动轴节点：同 timelineId 多行组成一条轴；行动推进时触发 prevDay &lt; day &lt;= newDay 且未触发过的节点，并按 day 升序结算。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>TbHiddenScoreCurve</t>
+          <t>TbGlobalConst</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>HiddenScoreCurve</t>
+          <t>GlobalConst</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>hidden_score_curve@reward_curve.xlsx</t>
+          <t>globalconst.xlsx</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
@@ -1733,19 +1733,19 @@
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>隐藏分曲线：基础隐藏分与派生隐藏分。</t>
+          <t>GlobalConst：跑通 Luban 接入用的占位表（与玩法无关）。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>TbGoldRewardCurve</t>
+          <t>TbHiddenScoreCurve</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>GoldRewardCurve</t>
+          <t>HiddenScoreCurve</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>gold_reward_curve@reward_curve.xlsx</t>
+          <t>hidden_score_curve@reward_curve.xlsx</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
@@ -1765,19 +1765,19 @@
       </c>
       <c r="I22" s="0" t="inlineStr">
         <is>
-          <t>金币奖励曲线：按进度和行动难度计算上下限。</t>
+          <t>隐藏分曲线：基础隐藏分与派生隐藏分。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>TbActionScheduleRule</t>
+          <t>TbGoldRewardCurve</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>ActionScheduleRule</t>
+          <t>GoldRewardCurve</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>action_schedule_rule@action.xlsx</t>
+          <t>gold_reward_curve@reward_curve.xlsx</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
@@ -1797,19 +1797,19 @@
       </c>
       <c r="I23" s="0" t="inlineStr">
         <is>
-          <t>整局行动日程规则：按整局行动序号窗口和优先级填充行动组序列。</t>
+          <t>金币奖励曲线：按进度和行动难度计算上下限。</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>TbUnlockRule</t>
+          <t>TbActionScheduleRule</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>UnlockRule</t>
+          <t>ActionScheduleRule</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>unlock_rule@unlock.xlsx</t>
+          <t>action_schedule_rule@action.xlsx</t>
         </is>
       </c>
       <c r="F24" s="0" t="inlineStr">
@@ -1829,19 +1829,19 @@
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t>解锁规则：一条规则定义一个跨局可解锁目标。</t>
+          <t>整局行动日程规则：按整局行动序号窗口和优先级填充行动组序列。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>TbUnlockCondition</t>
+          <t>TbUnlockRule</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>UnlockCondition</t>
+          <t>UnlockRule</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>unlock_condition@unlock.xlsx</t>
+          <t>unlock_rule@unlock.xlsx</t>
         </is>
       </c>
       <c r="F25" s="0" t="inlineStr">
@@ -1861,19 +1861,19 @@
       </c>
       <c r="I25" s="0" t="inlineStr">
         <is>
-          <t>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</t>
+          <t>解锁规则：一条规则定义一个跨局可解锁目标。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>TbSkill</t>
+          <t>TbUnlockCondition</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>UnlockCondition</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>skill@dish.xlsx</t>
+          <t>unlock_condition@unlock.xlsx</t>
         </is>
       </c>
       <c r="F26" s="0" t="inlineStr">
@@ -1893,19 +1893,19 @@
       </c>
       <c r="I26" s="0" t="inlineStr">
         <is>
-          <t>菜品技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</t>
+          <t>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>TbFlavor</t>
+          <t>TbSkill</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>Flavor</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>flavor@dish.xlsx</t>
+          <t>skill@dish.xlsx</t>
         </is>
       </c>
       <c r="F27" s="0" t="inlineStr">
@@ -1925,19 +1925,19 @@
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t>菜品风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</t>
+          <t>菜品技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>TbMaterial</t>
+          <t>TbFlavor</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Flavor</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>material@fragment_material.xlsx</t>
+          <t>flavor@dish.xlsx</t>
         </is>
       </c>
       <c r="F28" s="0" t="inlineStr">
@@ -1957,19 +1957,19 @@
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t>餐桌材质：挂在餐桌碎片格上（TbFragmentMaterial 引用）。effectType/effectValue 定义结算效果。</t>
+          <t>菜品风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>TbCakeLayerBuff</t>
+          <t>TbMaterial</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>CakeLayerBuff</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>cake_layer_buff@dish.xlsx</t>
+          <t>material@fragment_material.xlsx</t>
         </is>
       </c>
       <c r="F29" s="0" t="inlineStr">
@@ -1989,19 +1989,19 @@
       </c>
       <c r="I29" s="0" t="inlineStr">
         <is>
-          <t>欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</t>
+          <t>餐桌材质：挂在餐桌碎片格上（TbFragmentMaterial 引用）。effectType/effectValue 定义结算效果。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>TbSubSkill</t>
+          <t>TbCakeLayerBuff</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>SubSkill</t>
+          <t>CakeLayerBuff</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>sub_skill@dish.xlsx</t>
+          <t>cake_layer_buff@dish.xlsx</t>
         </is>
       </c>
       <c r="F30" s="0" t="inlineStr">
@@ -2021,19 +2021,19 @@
       </c>
       <c r="I30" s="0" t="inlineStr">
         <is>
-          <t>子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + isPassive/signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</t>
+          <t>欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>TbFood</t>
+          <t>TbSubSkill</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>Food</t>
+          <t>SubSkill</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>food@food.xlsx</t>
+          <t>sub_skill@dish.xlsx</t>
         </is>
       </c>
       <c r="F31" s="0" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>美食/战斗明细（含 Boss）：Food 行动 foodId 关联；Boss=isBoss，按角色池/解锁条件随机。</t>
+          <t>子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + isPassive/signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>TbBossDebuff</t>
+          <t>TbFood</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>BossDebuff</t>
+          <t>Food</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>boss_debuff@food.xlsx</t>
+          <t>food@food.xlsx</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
@@ -2085,19 +2085,19 @@
       </c>
       <c r="I32" s="0" t="inlineStr">
         <is>
-          <t>Boss 盛宴 Debuff：Boss 美食战斗独立抽取，不放回随机；抽空后重置历史。</t>
+          <t>美食/战斗明细（含 Boss）：Food 行动 foodId 关联；Boss=isBoss，按角色池/解锁条件随机。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>TbEvent</t>
+          <t>TbBossDebuff</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>GameEvent</t>
+          <t>BossDebuff</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>event@event.xlsx</t>
+          <t>boss_debuff@food.xlsx</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
@@ -2117,19 +2117,19 @@
       </c>
       <c r="I33" s="0" t="inlineStr">
         <is>
-          <t>事件明细：eventType 分类(Event/Reward/Negative)，公共 preconditions/weight/repeatable。</t>
+          <t>Boss 盛宴 Debuff：Boss 美食战斗独立抽取，不放回随机；抽空后重置历史。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>TbEventOption</t>
+          <t>TbEvent</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>EventOption</t>
+          <t>GameEvent</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>event_option@event.xlsx</t>
+          <t>event@event.xlsx</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
@@ -2149,19 +2149,19 @@
       </c>
       <c r="I34" s="0" t="inlineStr">
         <is>
-          <t>事件选项：同 eventId 多行=选项分支；单选项=自动结算。effectType 用 EffectType。</t>
+          <t>事件明细：eventType 分类(Event/Reward/Negative)，公共 preconditions/weight/repeatable。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>TbActionSmallGroup</t>
+          <t>TbEventOption</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>ActionSmallGroup</t>
+          <t>EventOption</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>small_group@action.xlsx</t>
+          <t>event_option@event.xlsx</t>
         </is>
       </c>
       <c r="F35" s="0" t="inlineStr">
@@ -2181,19 +2181,19 @@
       </c>
       <c r="I35" s="0" t="inlineStr">
         <is>
-          <t>小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选；weight 供大组挑选。</t>
+          <t>事件选项：同 eventId 多行=选项分支；单选项=自动结算。effectType 用 EffectType。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>TbActionLargeGroup</t>
+          <t>TbActionSmallGroup</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>ActionLargeGroup</t>
+          <t>ActionSmallGroup</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>large_group@action.xlsx</t>
+          <t>small_group@action.xlsx</t>
         </is>
       </c>
       <c r="F36" s="0" t="inlineStr">
@@ -2213,38 +2213,70 @@
       </c>
       <c r="I36" s="0" t="inlineStr">
         <is>
-          <t>行动大组：内嵌 smallGroupIds(list,string)，按保底权重与日程规则参与随机。</t>
+          <t>小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选；weight 供大组挑选。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
         <is>
+          <t>TbActionLargeGroup</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>ActionLargeGroup</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>large_group@action.xlsx</t>
+        </is>
+      </c>
+      <c r="F37" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>行动大组：内嵌 smallGroupIds(list,string)，按保底权重与日程规则参与随机。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="0" t="inlineStr">
+        <is>
           <t>TbGameBase</t>
         </is>
       </c>
-      <c r="C37" s="0" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>GameBase</t>
         </is>
       </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>game_base.xlsx</t>
         </is>
       </c>
-      <c r="F37" s="0" t="n"/>
-      <c r="G37" s="0" t="inlineStr">
+      <c r="F38" s="0" t="n"/>
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
-      <c r="I37" s="0" t="inlineStr">
+      <c r="I38" s="0" t="inlineStr">
         <is>
           <t>全局基础配置：整局初始金币、利息与食物调整等基础数值。</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>reward_package@timeline.xlsx</t>
+          <t>reward_package@reward.xlsx</t>
         </is>
       </c>
       <c r="F14" s="0" t="inlineStr">
@@ -1507,9 +1507,10 @@
           <t>id</t>
         </is>
       </c>
+      <c r="H14" s="0" t="n"/>
       <c r="I14" s="0" t="inlineStr">
         <is>
-          <t>奖励包：与 week 同在 timeline.xlsx；Week.rewardPackageId/Action.rewardPackageId 引用它，槽组继续指向 reward.xlsx/reward_slot。</t>
+          <t>奖励包：与奖励槽/奖励池同在 reward.xlsx；Week.rewardPackageId/Action.rewardPackageId 引用它，槽组指向 reward_slot。</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1572,9 +1572,9 @@
           <t>id</t>
         </is>
       </c>
-      <c r="I16" s="0" t="inlineStr">
-        <is>
-          <t>奖励池筛选：qualityWeights 写 Common:70|Uncommon:25|Rare:5；specialTags 用 | 分隔。</t>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>奖励池筛选：specialTags 用 | 分隔；道具不按品质权重筛选。</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -1735,7 +1735,7 @@
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>金币奖励曲线：按进度和行动难度计算上下限。</t>
+          <t>金币奖励曲线：按进度计算中心值，并按 fluctuationPct 浮动取值。</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R65fb57387f324e5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf97cfe7d49c749ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2039,10 +2039,8 @@
           <x:t xml:space="preserve">one</x:t>
         </x:is>
       </x:c>
-      <x:c r="I36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">全局基础配置：整局初始金币、利息与食物调整等基础数值。</x:t>
-        </x:is>
+      <x:c r="I36" t="str">
+        <x:v>全局基础配置：整局初始金币、利息与商店等基础数值。</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -2085,8 +2083,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Re8a3383792764e82"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Rf577e4b7b01447a4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Rfb52f92c3cda4176"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="R2be849da7d7142f8"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf97cfe7d49c749ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7b2f1d45c7084168"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1245,826 +1245,640 @@
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="B12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbScoreProfile</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ScoreProfile</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">score_profile@timeline.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">目标分曲线：与 week 同在 timeline.xlsx；Week.scoreProfileId/Boss.scoreProfileId 引用它生成普通与 Boss 目标分。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
+        <x:v>TbRewardPackage</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>RewardPackage</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>reward_package@reward.xlsx</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12" t="str">
+        <x:v>奖励包：与奖励槽/奖励池同在 reward.xlsx；Food.rewardPackageId 引用它，槽组指向 reward_slot。</x:v>
+      </x:c>
+      <x:c r="J12"/>
+      <x:c r="K12"/>
     </x:row>
     <x:row r="13">
-      <x:c r="B13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbRewardPackage</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RewardPackage</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reward_package@reward.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">奖励包：与奖励槽/奖励池同在 reward.xlsx；Week.rewardPackageId/Action.rewardPackageId 引用它，槽组指向 reward_slot。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
+        <x:v>TbRewardSlot</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>RewardSlot</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>reward_slot@reward.xlsx</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13" t="str">
+        <x:v>奖励槽：同 groupId 内按 weight 选一个槽，再按槽规则生成候选。</x:v>
+      </x:c>
+      <x:c r="J13"/>
+      <x:c r="K13"/>
     </x:row>
     <x:row r="14">
-      <x:c r="B14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbRewardSlot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RewardSlot</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reward_slot@reward.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">奖励槽：同 groupId 内按 weight 选一个槽，再按槽规则生成候选。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A14"/>
+      <x:c r="B14" t="str">
+        <x:v>TbRewardPool</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>RewardPool</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>reward_pool@reward.xlsx</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14" t="str">
+        <x:v>奖励池筛选：specialTags 用 | 分隔；道具不按品质权重筛选。</x:v>
+      </x:c>
+      <x:c r="J14"/>
+      <x:c r="K14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="B15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbRewardPool</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RewardPool</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">reward_pool@reward.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">奖励池筛选：specialTags 用 | 分隔；道具不按品质权重筛选。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A15"/>
+      <x:c r="B15" t="str">
+        <x:v>TbWeek</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>Week</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>week@timeline.xlsx</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15" t="str">
+        <x:v>周/关卡配置：定义每周修饰符、候选行动轴列表与行动轴权重。</x:v>
+      </x:c>
+      <x:c r="J15"/>
+      <x:c r="K15"/>
     </x:row>
     <x:row r="16">
-      <x:c r="B16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbWeek</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Week</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">week@timeline.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">周/关卡配置：定义每周的目标分曲线、默认奖励包、奖励隐藏分、候选行动轴列表与行动轴权重。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A16"/>
+      <x:c r="B16" t="str">
+        <x:v>TbAction</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>GameAction</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>action@action.xlsx</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G16"/>
+      <x:c r="H16"/>
+      <x:c r="I16" t="str">
+        <x:v>行动（薄壳分派）：只留 behavior 与关联/少量参数；具体内容在 TbFood/TbEvent。</x:v>
+      </x:c>
+      <x:c r="J16"/>
+      <x:c r="K16"/>
     </x:row>
     <x:row r="17">
-      <x:c r="B17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbAction</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GameAction</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">action@action.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">行动（薄壳分派）：只留 behavior 与关联/少量参数；具体内容在 TbFood/TbEvent。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A17"/>
+      <x:c r="B17" t="str">
+        <x:v>TbTimeline</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Timeline</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>timeline@timeline.xlsx</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G17"/>
+      <x:c r="H17"/>
+      <x:c r="I17" t="str">
+        <x:v>行动轴库：定义行动轴模板与基础长度；具体每周候选池和权重由 Week.timelineIds/timelineWeights 决定。</x:v>
+      </x:c>
+      <x:c r="J17"/>
+      <x:c r="K17"/>
     </x:row>
     <x:row r="18">
-      <x:c r="B18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbTimeline</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Timeline</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">timeline@timeline.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">行动轴库：定义行动轴模板与基础长度；具体每周候选池和权重由 Week.timelineIds/timelineWeights 决定。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A18"/>
+      <x:c r="B18" t="str">
+        <x:v>TbTimelineNode</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>TimelineNode</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>timeline_node@timeline.xlsx</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G18"/>
+      <x:c r="H18"/>
+      <x:c r="I18" t="str">
+        <x:v>行动轴节点：同 timelineId 多行组成一条轴；行动推进时触发 prevDay &lt; day &lt;= newDay 且未触发过的节点，并按 day 升序结算。</x:v>
+      </x:c>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="B19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbTimelineNode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TimelineNode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">timeline_node@timeline.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">行动轴节点：同 timelineId 多行组成一条轴；行动推进时触发 prevDay &lt; day &lt;= newDay 且未触发过的节点，并按 day 升序结算。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A19"/>
+      <x:c r="B19" t="str">
+        <x:v>TbHiddenScoreCurve</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>HiddenScoreCurve</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>hidden_score_curve@curve.xlsx</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G19"/>
+      <x:c r="H19"/>
+      <x:c r="I19" t="str">
+        <x:v>隐藏分曲线：基础隐藏分与派生隐藏分。</x:v>
+      </x:c>
+      <x:c r="J19"/>
+      <x:c r="K19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="B20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbHiddenScoreCurve</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HiddenScoreCurve</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E20" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">hidden_score_curve@curve.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">隐藏分曲线：基础隐藏分与派生隐藏分。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A20"/>
+      <x:c r="B20" t="str">
+        <x:v>TbGoldRewardCurve</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>GoldRewardCurve</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="str">
+        <x:v>gold_reward_curve@curve.xlsx</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+      <x:c r="I20" t="str">
+        <x:v>金币奖励曲线：按进度计算中心值，并按 fluctuationPct 浮动取值。</x:v>
+      </x:c>
+      <x:c r="J20"/>
+      <x:c r="K20"/>
     </x:row>
     <x:row r="21">
-      <x:c r="B21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbGoldRewardCurve</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GoldRewardCurve</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E21" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">gold_reward_curve@curve.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">金币奖励曲线：按进度计算中心值，并按 fluctuationPct 浮动取值。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A21"/>
+      <x:c r="B21" t="str">
+        <x:v>TbActionScheduleRule</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>ActionScheduleRule</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E21" s="2" t="str">
+        <x:v>action_schedule_rule@action.xlsx</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
+      <x:c r="I21" t="str">
+        <x:v>整局行动日程规则：按整局行动序号窗口和优先级填充行动组序列。</x:v>
+      </x:c>
+      <x:c r="J21"/>
+      <x:c r="K21"/>
     </x:row>
     <x:row r="22">
-      <x:c r="B22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbActionScheduleRule</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ActionScheduleRule</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">action_schedule_rule@action.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">整局行动日程规则：按整局行动序号窗口和优先级填充行动组序列。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A22"/>
+      <x:c r="B22" t="str">
+        <x:v>TbUnlockRule</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>UnlockRule</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>unlock_rule@unlock.xlsx</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G22"/>
+      <x:c r="H22"/>
+      <x:c r="I22" t="str">
+        <x:v>解锁规则：一条规则定义一个跨局可解锁目标。</x:v>
+      </x:c>
+      <x:c r="J22"/>
+      <x:c r="K22"/>
     </x:row>
     <x:row r="23">
-      <x:c r="B23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbUnlockRule</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">UnlockRule</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">unlock_rule@unlock.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">解锁规则：一条规则定义一个跨局可解锁目标。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A23"/>
+      <x:c r="B23" t="str">
+        <x:v>TbUnlockCondition</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>UnlockCondition</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>unlock_condition@unlock.xlsx</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G23"/>
+      <x:c r="H23"/>
+      <x:c r="I23" t="str">
+        <x:v>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</x:v>
+      </x:c>
+      <x:c r="J23"/>
+      <x:c r="K23"/>
     </x:row>
     <x:row r="24">
-      <x:c r="B24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbUnlockCondition</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">UnlockCondition</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">unlock_condition@unlock.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A24"/>
+      <x:c r="B24" t="str">
+        <x:v>TbSkill</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Skill</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>skill@dish.xlsx</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G24"/>
+      <x:c r="H24"/>
+      <x:c r="I24" t="str">
+        <x:v>菜品技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</x:v>
+      </x:c>
+      <x:c r="J24"/>
+      <x:c r="K24"/>
     </x:row>
     <x:row r="25">
-      <x:c r="B25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbSkill</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Skill</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">skill@dish.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">菜品技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A25"/>
+      <x:c r="B25" t="str">
+        <x:v>TbFlavor</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Flavor</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>flavor@dish.xlsx</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G25"/>
+      <x:c r="H25"/>
+      <x:c r="I25" t="str">
+        <x:v>菜品风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</x:v>
+      </x:c>
+      <x:c r="J25"/>
+      <x:c r="K25"/>
     </x:row>
     <x:row r="26">
-      <x:c r="B26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbFlavor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Flavor</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flavor@dish.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">菜品风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A26"/>
+      <x:c r="B26" t="str">
+        <x:v>TbMaterial</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>Material</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>material@fragment_material.xlsx</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G26"/>
+      <x:c r="H26"/>
+      <x:c r="I26" t="str">
+        <x:v>餐桌材质：挂在餐桌碎片格上（TableFragment.materialIds 引用）。effectType/effectValue 定义结算效果。</x:v>
+      </x:c>
+      <x:c r="J26"/>
+      <x:c r="K26"/>
     </x:row>
     <x:row r="27">
-      <x:c r="B27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbMaterial</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Material</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">material@fragment_material.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">餐桌材质：挂在餐桌碎片格上（TableFragment.materialIds 引用）。effectType/effectValue 定义结算效果。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A27"/>
+      <x:c r="B27" t="str">
+        <x:v>TbCakeLayerBuff</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>CakeLayerBuff</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>cake_layer_buff@dish.xlsx</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G27"/>
+      <x:c r="H27"/>
+      <x:c r="I27" t="str">
+        <x:v>欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</x:v>
+      </x:c>
+      <x:c r="J27"/>
+      <x:c r="K27"/>
     </x:row>
     <x:row r="28">
-      <x:c r="B28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbCakeLayerBuff</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CakeLayerBuff</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">cake_layer_buff@dish.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A28"/>
+      <x:c r="B28" t="str">
+        <x:v>TbSubSkill</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>SubSkill</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>sub_skill@dish.xlsx</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G28"/>
+      <x:c r="H28"/>
+      <x:c r="I28" t="str">
+        <x:v>子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + isPassive/signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</x:v>
+      </x:c>
+      <x:c r="J28"/>
+      <x:c r="K28"/>
     </x:row>
     <x:row r="29">
-      <x:c r="B29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbSubSkill</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SubSkill</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">sub_skill@dish.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + isPassive/signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A29"/>
+      <x:c r="B29" t="str">
+        <x:v>TbFood</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>Food</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>food@food.xlsx</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+      <x:c r="I29" t="str">
+        <x:v>美食/战斗明细：Food 行动 foodId 关联；actionKind 区分普通/超级/盛宴 Boss。</x:v>
+      </x:c>
+      <x:c r="J29"/>
+      <x:c r="K29"/>
     </x:row>
     <x:row r="30">
-      <x:c r="B30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbFood</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Food</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">food@food.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">美食/战斗明细：Food 行动 foodId 关联；actionKind 区分普通/超级/盛宴 Boss。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A30"/>
+      <x:c r="B30" t="str">
+        <x:v>TbBossDebuff</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>BossDebuff</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>boss_debuff@food.xlsx</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+      <x:c r="I30" t="str">
+        <x:v>Boss 盛宴 Debuff：Boss 美食战斗独立抽取，不放回随机；抽空后重置历史。</x:v>
+      </x:c>
+      <x:c r="J30"/>
+      <x:c r="K30"/>
     </x:row>
     <x:row r="31">
-      <x:c r="B31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbBossDebuff</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BossDebuff</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">boss_debuff@food.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Boss 盛宴 Debuff：Boss 美食战斗独立抽取，不放回随机；抽空后重置历史。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A31"/>
+      <x:c r="B31" t="str">
+        <x:v>TbEvent</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>GameEvent</x:v>
+      </x:c>
+      <x:c r="D31" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E31" t="str">
+        <x:v>event@event.xlsx</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G31"/>
+      <x:c r="H31"/>
+      <x:c r="I31" t="str">
+        <x:v>事件明细：eventType 分类(Event/Reward/Negative)，公共 preconditions/weight/repeatable。</x:v>
+      </x:c>
+      <x:c r="J31"/>
+      <x:c r="K31"/>
     </x:row>
     <x:row r="32">
-      <x:c r="B32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbEvent</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GameEvent</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">event@event.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">事件明细：eventType 分类(Event/Reward/Negative)，公共 preconditions/weight/repeatable。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A32"/>
+      <x:c r="B32" t="str">
+        <x:v>TbEventOption</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>EventOption</x:v>
+      </x:c>
+      <x:c r="D32" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E32" t="str">
+        <x:v>event_option@event.xlsx</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G32"/>
+      <x:c r="H32"/>
+      <x:c r="I32" t="str">
+        <x:v>事件选项：同 eventId 多行=选项分支；单选项=自动结算。effectType 用 EffectType。</x:v>
+      </x:c>
+      <x:c r="J32"/>
+      <x:c r="K32"/>
     </x:row>
     <x:row r="33">
-      <x:c r="B33" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbEventOption</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C33" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EventOption</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D33" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E33" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">event_option@event.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F33" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I33" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">事件选项：同 eventId 多行=选项分支；单选项=自动结算。effectType 用 EffectType。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A33"/>
+      <x:c r="B33" t="str">
+        <x:v>TbActionSmallGroup</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>ActionSmallGroup</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>small_group@action.xlsx</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G33"/>
+      <x:c r="H33"/>
+      <x:c r="I33" t="str">
+        <x:v>小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选；weight 供大组挑选。</x:v>
+      </x:c>
+      <x:c r="J33"/>
+      <x:c r="K33"/>
     </x:row>
     <x:row r="34">
-      <x:c r="B34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbActionSmallGroup</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ActionSmallGroup</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">small_group@action.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选；weight 供大组挑选。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A34"/>
+      <x:c r="B34" t="str">
+        <x:v>TbActionLargeGroup</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>ActionLargeGroup</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>large_group@action.xlsx</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G34"/>
+      <x:c r="H34"/>
+      <x:c r="I34" t="str">
+        <x:v>行动大组：内嵌 smallGroupIds(list,string)，按保底权重与日程规则参与随机。</x:v>
+      </x:c>
+      <x:c r="J34"/>
+      <x:c r="K34"/>
     </x:row>
     <x:row r="35">
-      <x:c r="B35" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbActionLargeGroup</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C35" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ActionLargeGroup</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D35" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E35" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">large_group@action.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F35" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I35" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">行动大组：内嵌 smallGroupIds(list,string)，按保底权重与日程规则参与随机。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A35"/>
+      <x:c r="B35" t="str">
+        <x:v>TbGameBase</x:v>
+      </x:c>
+      <x:c r="C35" t="str">
+        <x:v>GameBase</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E35" t="str">
+        <x:v>game_base.xlsx</x:v>
+      </x:c>
+      <x:c r="F35"/>
+      <x:c r="G35" t="str">
+        <x:v>one</x:v>
+      </x:c>
+      <x:c r="H35"/>
+      <x:c r="I35" t="str">
+        <x:v>全局基础配置：整局初始金币、利息与商店等基础数值。</x:v>
+      </x:c>
+      <x:c r="J35"/>
+      <x:c r="K35"/>
     </x:row>
     <x:row r="36">
-      <x:c r="B36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbGameBase</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GameBase</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">game_base.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F36" t="n"/>
-      <x:c r="G36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">one</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A36"/>
+      <x:c r="B36" t="str">
+        <x:v>TbRecipeGroup</x:v>
+      </x:c>
+      <x:c r="C36" t="str">
+        <x:v>RecipeGroup</x:v>
+      </x:c>
+      <x:c r="D36" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E36" t="str">
+        <x:v>recipe_group@recipe.xlsx</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G36"/>
+      <x:c r="H36"/>
       <x:c r="I36" t="str">
-        <x:v>全局基础配置：整局初始金币、利息与商店等基础数值。</x:v>
-      </x:c>
+        <x:v>菜谱随机小组：仅配置组ID与组内带权放回随机池，菜谱通过 groupIds 正向引用。</x:v>
+      </x:c>
+      <x:c r="J36"/>
+      <x:c r="K36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37"/>
-      <x:c r="B37" t="str">
-        <x:v>TbRecipeGroup</x:v>
-      </x:c>
-      <x:c r="C37" t="str">
-        <x:v>RecipeGroup</x:v>
-      </x:c>
-      <x:c r="D37" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E37" t="str">
-        <x:v>recipe_group@recipe.xlsx</x:v>
-      </x:c>
-      <x:c r="F37" t="str">
-        <x:v>id</x:v>
-      </x:c>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
       <x:c r="G37"/>
       <x:c r="H37"/>
-      <x:c r="I37" t="str">
-        <x:v>菜谱随机小组：仅配置组ID与组内带权放回随机池，菜谱通过 groupIds 正向引用。</x:v>
-      </x:c>
+      <x:c r="I37"/>
       <x:c r="J37"/>
       <x:c r="K37"/>
     </x:row>
@@ -2083,8 +1897,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Rfb52f92c3cda4176"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="R2be849da7d7142f8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Rf58acfa03ad74ad1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="R73a736d5f3cf4de6"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7b2f1d45c7084168"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R818d31bf96664669"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1397,16 +1397,16 @@
     <x:row r="18">
       <x:c r="A18"/>
       <x:c r="B18" t="str">
-        <x:v>TbTimelineNode</x:v>
+        <x:v>TbHiddenScoreCurve</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>TimelineNode</x:v>
+        <x:v>HiddenScoreCurve</x:v>
       </x:c>
       <x:c r="D18" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E18" t="str">
-        <x:v>timeline_node@timeline.xlsx</x:v>
+        <x:v>hidden_score_curve@curve.xlsx</x:v>
       </x:c>
       <x:c r="F18" t="str">
         <x:v>id</x:v>
@@ -1414,7 +1414,7 @@
       <x:c r="G18"/>
       <x:c r="H18"/>
       <x:c r="I18" t="str">
-        <x:v>行动轴节点：同 timelineId 多行组成一条轴；行动推进时触发 prevDay &lt; day &lt;= newDay 且未触发过的节点，并按 day 升序结算。</x:v>
+        <x:v>隐藏分曲线：基础隐藏分与派生隐藏分。</x:v>
       </x:c>
       <x:c r="J18"/>
       <x:c r="K18"/>
@@ -1422,16 +1422,16 @@
     <x:row r="19">
       <x:c r="A19"/>
       <x:c r="B19" t="str">
-        <x:v>TbHiddenScoreCurve</x:v>
+        <x:v>TbGoldRewardCurve</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>HiddenScoreCurve</x:v>
+        <x:v>GoldRewardCurve</x:v>
       </x:c>
       <x:c r="D19" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E19" t="str">
-        <x:v>hidden_score_curve@curve.xlsx</x:v>
+        <x:v>gold_reward_curve@curve.xlsx</x:v>
       </x:c>
       <x:c r="F19" t="str">
         <x:v>id</x:v>
@@ -1439,7 +1439,7 @@
       <x:c r="G19"/>
       <x:c r="H19"/>
       <x:c r="I19" t="str">
-        <x:v>隐藏分曲线：基础隐藏分与派生隐藏分。</x:v>
+        <x:v>金币奖励曲线：按进度计算中心值，并按 fluctuationPct 浮动取值。</x:v>
       </x:c>
       <x:c r="J19"/>
       <x:c r="K19"/>
@@ -1447,16 +1447,16 @@
     <x:row r="20">
       <x:c r="A20"/>
       <x:c r="B20" t="str">
-        <x:v>TbGoldRewardCurve</x:v>
+        <x:v>TbActionScheduleRule</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>GoldRewardCurve</x:v>
+        <x:v>ActionScheduleRule</x:v>
       </x:c>
       <x:c r="D20" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E20" s="1" t="str">
-        <x:v>gold_reward_curve@curve.xlsx</x:v>
+        <x:v>action_schedule_rule@action.xlsx</x:v>
       </x:c>
       <x:c r="F20" t="str">
         <x:v>id</x:v>
@@ -1464,7 +1464,7 @@
       <x:c r="G20"/>
       <x:c r="H20"/>
       <x:c r="I20" t="str">
-        <x:v>金币奖励曲线：按进度计算中心值，并按 fluctuationPct 浮动取值。</x:v>
+        <x:v>整局行动日程规则：按整局行动序号窗口和优先级填充行动组序列。</x:v>
       </x:c>
       <x:c r="J20"/>
       <x:c r="K20"/>
@@ -1472,16 +1472,16 @@
     <x:row r="21">
       <x:c r="A21"/>
       <x:c r="B21" t="str">
-        <x:v>TbActionScheduleRule</x:v>
+        <x:v>TbUnlockRule</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>ActionScheduleRule</x:v>
+        <x:v>UnlockRule</x:v>
       </x:c>
       <x:c r="D21" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E21" s="2" t="str">
-        <x:v>action_schedule_rule@action.xlsx</x:v>
+        <x:v>unlock_rule@unlock.xlsx</x:v>
       </x:c>
       <x:c r="F21" t="str">
         <x:v>id</x:v>
@@ -1489,7 +1489,7 @@
       <x:c r="G21"/>
       <x:c r="H21"/>
       <x:c r="I21" t="str">
-        <x:v>整局行动日程规则：按整局行动序号窗口和优先级填充行动组序列。</x:v>
+        <x:v>解锁规则：一条规则定义一个跨局可解锁目标。</x:v>
       </x:c>
       <x:c r="J21"/>
       <x:c r="K21"/>
@@ -1497,16 +1497,16 @@
     <x:row r="22">
       <x:c r="A22"/>
       <x:c r="B22" t="str">
-        <x:v>TbUnlockRule</x:v>
+        <x:v>TbUnlockCondition</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>UnlockRule</x:v>
+        <x:v>UnlockCondition</x:v>
       </x:c>
       <x:c r="D22" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E22" t="str">
-        <x:v>unlock_rule@unlock.xlsx</x:v>
+        <x:v>unlock_condition@unlock.xlsx</x:v>
       </x:c>
       <x:c r="F22" t="str">
         <x:v>id</x:v>
@@ -1514,7 +1514,7 @@
       <x:c r="G22"/>
       <x:c r="H22"/>
       <x:c r="I22" t="str">
-        <x:v>解锁规则：一条规则定义一个跨局可解锁目标。</x:v>
+        <x:v>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</x:v>
       </x:c>
       <x:c r="J22"/>
       <x:c r="K22"/>
@@ -1522,16 +1522,16 @@
     <x:row r="23">
       <x:c r="A23"/>
       <x:c r="B23" t="str">
-        <x:v>TbUnlockCondition</x:v>
+        <x:v>TbSkill</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>UnlockCondition</x:v>
+        <x:v>Skill</x:v>
       </x:c>
       <x:c r="D23" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E23" t="str">
-        <x:v>unlock_condition@unlock.xlsx</x:v>
+        <x:v>skill@dish.xlsx</x:v>
       </x:c>
       <x:c r="F23" t="str">
         <x:v>id</x:v>
@@ -1539,7 +1539,7 @@
       <x:c r="G23"/>
       <x:c r="H23"/>
       <x:c r="I23" t="str">
-        <x:v>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</x:v>
+        <x:v>菜品技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</x:v>
       </x:c>
       <x:c r="J23"/>
       <x:c r="K23"/>
@@ -1547,16 +1547,16 @@
     <x:row r="24">
       <x:c r="A24"/>
       <x:c r="B24" t="str">
-        <x:v>TbSkill</x:v>
+        <x:v>TbFlavor</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>Skill</x:v>
+        <x:v>Flavor</x:v>
       </x:c>
       <x:c r="D24" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E24" t="str">
-        <x:v>skill@dish.xlsx</x:v>
+        <x:v>flavor@dish.xlsx</x:v>
       </x:c>
       <x:c r="F24" t="str">
         <x:v>id</x:v>
@@ -1564,7 +1564,7 @@
       <x:c r="G24"/>
       <x:c r="H24"/>
       <x:c r="I24" t="str">
-        <x:v>菜品技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</x:v>
+        <x:v>菜品风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</x:v>
       </x:c>
       <x:c r="J24"/>
       <x:c r="K24"/>
@@ -1572,16 +1572,16 @@
     <x:row r="25">
       <x:c r="A25"/>
       <x:c r="B25" t="str">
-        <x:v>TbFlavor</x:v>
+        <x:v>TbMaterial</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>Flavor</x:v>
+        <x:v>Material</x:v>
       </x:c>
       <x:c r="D25" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E25" t="str">
-        <x:v>flavor@dish.xlsx</x:v>
+        <x:v>material@fragment_material.xlsx</x:v>
       </x:c>
       <x:c r="F25" t="str">
         <x:v>id</x:v>
@@ -1589,7 +1589,7 @@
       <x:c r="G25"/>
       <x:c r="H25"/>
       <x:c r="I25" t="str">
-        <x:v>菜品风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</x:v>
+        <x:v>餐桌材质：挂在餐桌碎片格上（TableFragment.materialIds 引用）。effectType/effectValue 定义结算效果。</x:v>
       </x:c>
       <x:c r="J25"/>
       <x:c r="K25"/>
@@ -1597,16 +1597,16 @@
     <x:row r="26">
       <x:c r="A26"/>
       <x:c r="B26" t="str">
-        <x:v>TbMaterial</x:v>
+        <x:v>TbCakeLayerBuff</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>Material</x:v>
+        <x:v>CakeLayerBuff</x:v>
       </x:c>
       <x:c r="D26" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>material@fragment_material.xlsx</x:v>
+        <x:v>cake_layer_buff@dish.xlsx</x:v>
       </x:c>
       <x:c r="F26" t="str">
         <x:v>id</x:v>
@@ -1614,7 +1614,7 @@
       <x:c r="G26"/>
       <x:c r="H26"/>
       <x:c r="I26" t="str">
-        <x:v>餐桌材质：挂在餐桌碎片格上（TableFragment.materialIds 引用）。effectType/effectValue 定义结算效果。</x:v>
+        <x:v>欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</x:v>
       </x:c>
       <x:c r="J26"/>
       <x:c r="K26"/>
@@ -1622,16 +1622,16 @@
     <x:row r="27">
       <x:c r="A27"/>
       <x:c r="B27" t="str">
-        <x:v>TbCakeLayerBuff</x:v>
+        <x:v>TbSubSkill</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>CakeLayerBuff</x:v>
+        <x:v>SubSkill</x:v>
       </x:c>
       <x:c r="D27" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>cake_layer_buff@dish.xlsx</x:v>
+        <x:v>sub_skill@dish.xlsx</x:v>
       </x:c>
       <x:c r="F27" t="str">
         <x:v>id</x:v>
@@ -1639,7 +1639,7 @@
       <x:c r="G27"/>
       <x:c r="H27"/>
       <x:c r="I27" t="str">
-        <x:v>欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</x:v>
+        <x:v>子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + isPassive/signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</x:v>
       </x:c>
       <x:c r="J27"/>
       <x:c r="K27"/>
@@ -1647,16 +1647,16 @@
     <x:row r="28">
       <x:c r="A28"/>
       <x:c r="B28" t="str">
-        <x:v>TbSubSkill</x:v>
+        <x:v>TbFood</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>SubSkill</x:v>
+        <x:v>Food</x:v>
       </x:c>
       <x:c r="D28" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>sub_skill@dish.xlsx</x:v>
+        <x:v>food@food.xlsx</x:v>
       </x:c>
       <x:c r="F28" t="str">
         <x:v>id</x:v>
@@ -1664,7 +1664,7 @@
       <x:c r="G28"/>
       <x:c r="H28"/>
       <x:c r="I28" t="str">
-        <x:v>子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + isPassive/signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</x:v>
+        <x:v>美食/战斗明细：Food 行动 foodId 关联；actionKind 区分普通/超级/盛宴 Boss。</x:v>
       </x:c>
       <x:c r="J28"/>
       <x:c r="K28"/>
@@ -1672,16 +1672,16 @@
     <x:row r="29">
       <x:c r="A29"/>
       <x:c r="B29" t="str">
-        <x:v>TbFood</x:v>
+        <x:v>TbBossDebuff</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>Food</x:v>
+        <x:v>BossDebuff</x:v>
       </x:c>
       <x:c r="D29" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>food@food.xlsx</x:v>
+        <x:v>boss_debuff@food.xlsx</x:v>
       </x:c>
       <x:c r="F29" t="str">
         <x:v>id</x:v>
@@ -1689,7 +1689,7 @@
       <x:c r="G29"/>
       <x:c r="H29"/>
       <x:c r="I29" t="str">
-        <x:v>美食/战斗明细：Food 行动 foodId 关联；actionKind 区分普通/超级/盛宴 Boss。</x:v>
+        <x:v>Boss 盛宴 Debuff：Boss 美食战斗独立抽取，不放回随机；抽空后重置历史。</x:v>
       </x:c>
       <x:c r="J29"/>
       <x:c r="K29"/>
@@ -1697,16 +1697,16 @@
     <x:row r="30">
       <x:c r="A30"/>
       <x:c r="B30" t="str">
-        <x:v>TbBossDebuff</x:v>
+        <x:v>TbEvent</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>BossDebuff</x:v>
+        <x:v>GameEvent</x:v>
       </x:c>
       <x:c r="D30" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E30" t="str">
-        <x:v>boss_debuff@food.xlsx</x:v>
+        <x:v>event@event.xlsx</x:v>
       </x:c>
       <x:c r="F30" t="str">
         <x:v>id</x:v>
@@ -1714,7 +1714,7 @@
       <x:c r="G30"/>
       <x:c r="H30"/>
       <x:c r="I30" t="str">
-        <x:v>Boss 盛宴 Debuff：Boss 美食战斗独立抽取，不放回随机；抽空后重置历史。</x:v>
+        <x:v>事件明细：eventType 分类(Event/Reward/Negative)，公共 preconditions/weight/repeatable。</x:v>
       </x:c>
       <x:c r="J30"/>
       <x:c r="K30"/>
@@ -1722,16 +1722,16 @@
     <x:row r="31">
       <x:c r="A31"/>
       <x:c r="B31" t="str">
-        <x:v>TbEvent</x:v>
+        <x:v>TbEventOption</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>GameEvent</x:v>
+        <x:v>EventOption</x:v>
       </x:c>
       <x:c r="D31" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>event@event.xlsx</x:v>
+        <x:v>event_option@event.xlsx</x:v>
       </x:c>
       <x:c r="F31" t="str">
         <x:v>id</x:v>
@@ -1739,7 +1739,7 @@
       <x:c r="G31"/>
       <x:c r="H31"/>
       <x:c r="I31" t="str">
-        <x:v>事件明细：eventType 分类(Event/Reward/Negative)，公共 preconditions/weight/repeatable。</x:v>
+        <x:v>事件选项：同 eventId 多行=选项分支；单选项=自动结算。effectType 用 EffectType。</x:v>
       </x:c>
       <x:c r="J31"/>
       <x:c r="K31"/>
@@ -1747,16 +1747,16 @@
     <x:row r="32">
       <x:c r="A32"/>
       <x:c r="B32" t="str">
-        <x:v>TbEventOption</x:v>
+        <x:v>TbActionSmallGroup</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>EventOption</x:v>
+        <x:v>ActionSmallGroup</x:v>
       </x:c>
       <x:c r="D32" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E32" t="str">
-        <x:v>event_option@event.xlsx</x:v>
+        <x:v>small_group@action.xlsx</x:v>
       </x:c>
       <x:c r="F32" t="str">
         <x:v>id</x:v>
@@ -1764,7 +1764,7 @@
       <x:c r="G32"/>
       <x:c r="H32"/>
       <x:c r="I32" t="str">
-        <x:v>事件选项：同 eventId 多行=选项分支；单选项=自动结算。effectType 用 EffectType。</x:v>
+        <x:v>小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选；weight 供大组挑选。</x:v>
       </x:c>
       <x:c r="J32"/>
       <x:c r="K32"/>
@@ -1772,16 +1772,16 @@
     <x:row r="33">
       <x:c r="A33"/>
       <x:c r="B33" t="str">
-        <x:v>TbActionSmallGroup</x:v>
+        <x:v>TbActionLargeGroup</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>ActionSmallGroup</x:v>
+        <x:v>ActionLargeGroup</x:v>
       </x:c>
       <x:c r="D33" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E33" t="str">
-        <x:v>small_group@action.xlsx</x:v>
+        <x:v>large_group@action.xlsx</x:v>
       </x:c>
       <x:c r="F33" t="str">
         <x:v>id</x:v>
@@ -1789,7 +1789,7 @@
       <x:c r="G33"/>
       <x:c r="H33"/>
       <x:c r="I33" t="str">
-        <x:v>小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选；weight 供大组挑选。</x:v>
+        <x:v>行动大组：内嵌 smallGroupIds(list,string)，按保底权重与日程规则参与随机。</x:v>
       </x:c>
       <x:c r="J33"/>
       <x:c r="K33"/>
@@ -1797,24 +1797,24 @@
     <x:row r="34">
       <x:c r="A34"/>
       <x:c r="B34" t="str">
-        <x:v>TbActionLargeGroup</x:v>
+        <x:v>TbGameBase</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>ActionLargeGroup</x:v>
+        <x:v>GameBase</x:v>
       </x:c>
       <x:c r="D34" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E34" t="str">
-        <x:v>large_group@action.xlsx</x:v>
-      </x:c>
-      <x:c r="F34" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G34"/>
+        <x:v>game_base.xlsx</x:v>
+      </x:c>
+      <x:c r="F34"/>
+      <x:c r="G34" t="str">
+        <x:v>one</x:v>
+      </x:c>
       <x:c r="H34"/>
       <x:c r="I34" t="str">
-        <x:v>行动大组：内嵌 smallGroupIds(list,string)，按保底权重与日程规则参与随机。</x:v>
+        <x:v>全局基础配置：整局初始金币、利息与商店等基础数值。</x:v>
       </x:c>
       <x:c r="J34"/>
       <x:c r="K34"/>
@@ -1822,50 +1822,38 @@
     <x:row r="35">
       <x:c r="A35"/>
       <x:c r="B35" t="str">
-        <x:v>TbGameBase</x:v>
+        <x:v>TbRecipeGroup</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>GameBase</x:v>
+        <x:v>RecipeGroup</x:v>
       </x:c>
       <x:c r="D35" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E35" t="str">
-        <x:v>game_base.xlsx</x:v>
-      </x:c>
-      <x:c r="F35"/>
-      <x:c r="G35" t="str">
-        <x:v>one</x:v>
-      </x:c>
+        <x:v>recipe_group@recipe.xlsx</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G35"/>
       <x:c r="H35"/>
       <x:c r="I35" t="str">
-        <x:v>全局基础配置：整局初始金币、利息与商店等基础数值。</x:v>
+        <x:v>菜谱随机小组：仅配置组ID与组内带权放回随机池，菜谱通过 groupIds 正向引用。</x:v>
       </x:c>
       <x:c r="J35"/>
       <x:c r="K35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36"/>
-      <x:c r="B36" t="str">
-        <x:v>TbRecipeGroup</x:v>
-      </x:c>
-      <x:c r="C36" t="str">
-        <x:v>RecipeGroup</x:v>
-      </x:c>
-      <x:c r="D36" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E36" t="str">
-        <x:v>recipe_group@recipe.xlsx</x:v>
-      </x:c>
-      <x:c r="F36" t="str">
-        <x:v>id</x:v>
-      </x:c>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
       <x:c r="G36"/>
       <x:c r="H36"/>
-      <x:c r="I36" t="str">
-        <x:v>菜谱随机小组：仅配置组ID与组内带权放回随机池，菜谱通过 groupIds 正向引用。</x:v>
-      </x:c>
+      <x:c r="I36"/>
       <x:c r="J36"/>
       <x:c r="K36"/>
     </x:row>
@@ -1897,8 +1885,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Rf58acfa03ad74ad1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="R73a736d5f3cf4de6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="R7b8e95c423b04a29"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Reb897202324b432f"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R818d31bf96664669"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf1decea2efaa4c15"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1339,7 +1339,7 @@
       <x:c r="G15"/>
       <x:c r="H15"/>
       <x:c r="I15" t="str">
-        <x:v>周/关卡配置：定义每周修饰符、候选行动轴列表与行动轴权重。</x:v>
+        <x:v>周/关卡配置：定义每周候选行动轴列表与行动轴权重。</x:v>
       </x:c>
       <x:c r="J15"/>
       <x:c r="K15"/>
@@ -1885,8 +1885,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="R7b8e95c423b04a29"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Reb897202324b432f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="R7b2bd38eccfc4ec1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="R820d365c000548e2"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf1decea2efaa4c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R77e5b40a0fc94305"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -847,402 +847,299 @@
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">full_name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">value_type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">read_schema_from_file</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">input</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">index</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">mode</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">group</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">comment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">tags</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">output</x:t>
-        </x:is>
+      <x:c r="A1" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>full_name</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>value_type</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>read_schema_from_file</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>input</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>index</x:v>
+      </x:c>
+      <x:c r="G1" t="str">
+        <x:v>mode</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>comment</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>tags</x:v>
+      </x:c>
+      <x:c r="K1" t="str">
+        <x:v>output</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">全名(包含模块和名字)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">记录类名</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">从excel读取定义</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">文件列表</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">表id字段</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">模式</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">分组</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">注释</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">输出文件名</x:t>
-        </x:is>
+      <x:c r="A2" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>全名(包含模块和名字)</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>记录类名</x:v>
+      </x:c>
+      <x:c r="D2" t="str">
+        <x:v>从excel读取定义</x:v>
+      </x:c>
+      <x:c r="E2" t="str">
+        <x:v>文件列表</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
+        <x:v>表id字段</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>模式</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>分组</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>注释</x:v>
+      </x:c>
+      <x:c r="J2"/>
+      <x:c r="K2" t="str">
+        <x:v>输出文件名</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">false时取已有定义，true为从excel标题头和属性栏读取定义</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">可以多个，以逗号','分隔</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">取值one|map|list，为空自动为map</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</x:t>
-        </x:is>
+      <x:c r="A3" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3" t="str">
+        <x:v>false时取已有定义，true为从excel标题头和属性栏读取定义</x:v>
+      </x:c>
+      <x:c r="E3" t="str">
+        <x:v>可以多个，以逗号','分隔</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
+        <x:v>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>取值one|map|list，为空自动为map</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</x:v>
+      </x:c>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3" t="str">
+        <x:v>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbDishBase</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DishBase</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">dish_base@dish.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">菜品本体：物理属性（id/name/deliciousness/icon/allowRotate/shapeRows）与固有技能（skills→TbSkill）。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A4"/>
+      <x:c r="B4" t="str">
+        <x:v>TbDishBase</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>DishBase</x:v>
+      </x:c>
+      <x:c r="D4" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E4" t="str">
+        <x:v>dish_base@dish.xlsx</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4" t="str">
+        <x:v>菜品本体：物理属性（id/name/deliciousness/icon/allowRotate/shapeRows）与固有技能（skills→TbSkill）。</x:v>
+      </x:c>
+      <x:c r="J4"/>
+      <x:c r="K4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="B5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbDishVariant</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DishVariant</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">dish_variant@dish.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">菜品变体：随机菜品库条目。引用本体+风味(flavorId→TbFlavor,单槽)+隐藏分/权重/价格。flavorId 空串=无风味。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A5"/>
+      <x:c r="B5" t="str">
+        <x:v>TbDishVariant</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>DishVariant</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>dish_variant@dish.xlsx</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G5"/>
+      <x:c r="H5"/>
+      <x:c r="I5" t="str">
+        <x:v>菜品变体：随机菜品库条目。引用本体+风味(flavorId→TbFlavor,单槽)+隐藏分/权重/价格。flavorId 空串=无风味。</x:v>
+      </x:c>
+      <x:c r="J5"/>
+      <x:c r="K5"/>
     </x:row>
     <x:row r="6">
-      <x:c r="B6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbTerm</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Term</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">term.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">专有名词：菜品详情右侧框单独解释。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A6"/>
+      <x:c r="B6" t="str">
+        <x:v>TbTerm</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Term</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>term.xlsx</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G6"/>
+      <x:c r="H6"/>
+      <x:c r="I6" t="str">
+        <x:v>专有名词：菜品详情右侧框单独解释。</x:v>
+      </x:c>
+      <x:c r="J6"/>
+      <x:c r="K6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="B7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbCharacter</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Character</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">character.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">角色：配置初始菜谱/胃形状/道具，并通过 timelinePool/bossPool 限制该角色可随机到的行动轴和 Boss。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A7"/>
+      <x:c r="B7" t="str">
+        <x:v>TbCharacter</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>Character</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>character.xlsx</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G7"/>
+      <x:c r="H7"/>
+      <x:c r="I7" t="str">
+        <x:v>角色：配置初始菜谱/胃形状/道具。</x:v>
+      </x:c>
+      <x:c r="J7"/>
+      <x:c r="K7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="B8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbTableFragment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TableFragment</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">table_fragment@fragment_material.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">餐桌碎片库：也用作初始餐桌形状来源。materialIds 为该碎片可随机落位的材质列表；碎片不旋转(1x2 与 2x1 视为两个碎片)。'X'=存在格。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A8"/>
+      <x:c r="B8" t="str">
+        <x:v>TbTableFragment</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>TableFragment</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>table_fragment@fragment_material.xlsx</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G8"/>
+      <x:c r="H8"/>
+      <x:c r="I8" t="str">
+        <x:v>餐桌碎片库：也用作初始餐桌形状来源。materialIds 为该碎片可随机落位的材质列表；碎片不旋转(1x2 与 2x1 视为两个碎片)。'X'=存在格。</x:v>
+      </x:c>
+      <x:c r="J8"/>
+      <x:c r="K8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="B9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbRecipe</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Recipe</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
+      <x:c r="A9"/>
+      <x:c r="B9" t="str">
+        <x:v>TbRecipe</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Recipe</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>True</x:v>
       </x:c>
       <x:c r="E9" t="str">
         <x:v>recipe@recipe.xlsx</x:v>
       </x:c>
-      <x:c r="F9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G9"/>
+      <x:c r="H9"/>
       <x:c r="I9" t="str">
         <x:v>菜谱：直接配置有序 groupIds 与带权数量方案 rollPlans；随机小组内容由 TbRecipeGroup 配置。</x:v>
       </x:c>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="B10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbPassiveItem</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PassiveItem</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">被动道具@item.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">被动道具：永久常驻/获得时生效，道具池按隐藏分筛选。specialTags 用 | 分隔，空串=无。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
+        <x:v>TbPassiveItem</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>PassiveItem</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>被动道具@item.xlsx</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G10"/>
+      <x:c r="H10"/>
+      <x:c r="I10" t="str">
+        <x:v>被动道具：永久常驻/获得时生效，道具池按隐藏分筛选。specialTags 用 | 分隔，空串=无。</x:v>
+      </x:c>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
     </x:row>
     <x:row r="11">
-      <x:c r="B11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TbActiveItem</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ActiveItem</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">True</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">主动道具@item.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">主动道具：一次性占全局消耗槽，玩家手动使用；不配置隐藏分区间。specialTags 用 | 分隔，空串=无。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
+        <x:v>TbActiveItem</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>ActiveItem</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>主动道具@item.xlsx</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11" t="str">
+        <x:v>主动道具：一次性占全局消耗槽，玩家手动使用；不配置隐藏分区间。specialTags 用 | 分隔，空串=无。</x:v>
+      </x:c>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12"/>
@@ -1885,8 +1782,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="R7b2bd38eccfc4ec1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="R820d365c000548e2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="R0477fcc8b96d44c9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Rb4198bd5f8f749e2"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R77e5b40a0fc94305"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R17fa6d07511e4108"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1611,7 +1611,7 @@
       <x:c r="G30"/>
       <x:c r="H30"/>
       <x:c r="I30" t="str">
-        <x:v>事件明细：eventType 分类(Event/Reward/Negative)，公共 preconditions/weight/repeatable。</x:v>
+        <x:v>事件明细：eventTypes 用 | 配置多个分类；首项决定权重/保底，全部分类参与对应事件池。公共 preconditions/weight/repeatable。</x:v>
       </x:c>
       <x:c r="J30"/>
       <x:c r="K30"/>
@@ -1782,8 +1782,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="R0477fcc8b96d44c9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Rb4198bd5f8f749e2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Rdfd94f2514e14fbe"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="R17699449759040f5"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R17fa6d07511e4108"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5ce1119519264d92"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1344,16 +1344,16 @@
     <x:row r="20">
       <x:c r="A20"/>
       <x:c r="B20" t="str">
-        <x:v>TbActionScheduleRule</x:v>
+        <x:v>TbUnlockRule</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>ActionScheduleRule</x:v>
+        <x:v>UnlockRule</x:v>
       </x:c>
       <x:c r="D20" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E20" s="1" t="str">
-        <x:v>action_schedule_rule@action.xlsx</x:v>
+        <x:v>unlock_rule@unlock.xlsx</x:v>
       </x:c>
       <x:c r="F20" t="str">
         <x:v>id</x:v>
@@ -1361,7 +1361,7 @@
       <x:c r="G20"/>
       <x:c r="H20"/>
       <x:c r="I20" t="str">
-        <x:v>整局行动日程规则：按整局行动序号窗口和优先级填充行动组序列。</x:v>
+        <x:v>解锁规则：一条规则定义一个跨局可解锁目标。</x:v>
       </x:c>
       <x:c r="J20"/>
       <x:c r="K20"/>
@@ -1369,16 +1369,16 @@
     <x:row r="21">
       <x:c r="A21"/>
       <x:c r="B21" t="str">
-        <x:v>TbUnlockRule</x:v>
+        <x:v>TbUnlockCondition</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>UnlockRule</x:v>
+        <x:v>UnlockCondition</x:v>
       </x:c>
       <x:c r="D21" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E21" s="2" t="str">
-        <x:v>unlock_rule@unlock.xlsx</x:v>
+        <x:v>unlock_condition@unlock.xlsx</x:v>
       </x:c>
       <x:c r="F21" t="str">
         <x:v>id</x:v>
@@ -1386,7 +1386,7 @@
       <x:c r="G21"/>
       <x:c r="H21"/>
       <x:c r="I21" t="str">
-        <x:v>解锁规则：一条规则定义一个跨局可解锁目标。</x:v>
+        <x:v>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</x:v>
       </x:c>
       <x:c r="J21"/>
       <x:c r="K21"/>
@@ -1394,16 +1394,16 @@
     <x:row r="22">
       <x:c r="A22"/>
       <x:c r="B22" t="str">
-        <x:v>TbUnlockCondition</x:v>
+        <x:v>TbSkill</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>UnlockCondition</x:v>
+        <x:v>Skill</x:v>
       </x:c>
       <x:c r="D22" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E22" t="str">
-        <x:v>unlock_condition@unlock.xlsx</x:v>
+        <x:v>skill@dish.xlsx</x:v>
       </x:c>
       <x:c r="F22" t="str">
         <x:v>id</x:v>
@@ -1411,7 +1411,7 @@
       <x:c r="G22"/>
       <x:c r="H22"/>
       <x:c r="I22" t="str">
-        <x:v>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</x:v>
+        <x:v>菜品技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</x:v>
       </x:c>
       <x:c r="J22"/>
       <x:c r="K22"/>
@@ -1419,16 +1419,16 @@
     <x:row r="23">
       <x:c r="A23"/>
       <x:c r="B23" t="str">
-        <x:v>TbSkill</x:v>
+        <x:v>TbFlavor</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>Skill</x:v>
+        <x:v>Flavor</x:v>
       </x:c>
       <x:c r="D23" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E23" t="str">
-        <x:v>skill@dish.xlsx</x:v>
+        <x:v>flavor@dish.xlsx</x:v>
       </x:c>
       <x:c r="F23" t="str">
         <x:v>id</x:v>
@@ -1436,7 +1436,7 @@
       <x:c r="G23"/>
       <x:c r="H23"/>
       <x:c r="I23" t="str">
-        <x:v>菜品技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</x:v>
+        <x:v>菜品风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</x:v>
       </x:c>
       <x:c r="J23"/>
       <x:c r="K23"/>
@@ -1444,16 +1444,16 @@
     <x:row r="24">
       <x:c r="A24"/>
       <x:c r="B24" t="str">
-        <x:v>TbFlavor</x:v>
+        <x:v>TbMaterial</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>Flavor</x:v>
+        <x:v>Material</x:v>
       </x:c>
       <x:c r="D24" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E24" t="str">
-        <x:v>flavor@dish.xlsx</x:v>
+        <x:v>material@fragment_material.xlsx</x:v>
       </x:c>
       <x:c r="F24" t="str">
         <x:v>id</x:v>
@@ -1461,7 +1461,7 @@
       <x:c r="G24"/>
       <x:c r="H24"/>
       <x:c r="I24" t="str">
-        <x:v>菜品风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</x:v>
+        <x:v>餐桌材质：挂在餐桌碎片格上（TableFragment.materialIds 引用）。effectType/effectValue 定义结算效果。</x:v>
       </x:c>
       <x:c r="J24"/>
       <x:c r="K24"/>
@@ -1469,16 +1469,16 @@
     <x:row r="25">
       <x:c r="A25"/>
       <x:c r="B25" t="str">
-        <x:v>TbMaterial</x:v>
+        <x:v>TbCakeLayerBuff</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>Material</x:v>
+        <x:v>CakeLayerBuff</x:v>
       </x:c>
       <x:c r="D25" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E25" t="str">
-        <x:v>material@fragment_material.xlsx</x:v>
+        <x:v>cake_layer_buff@dish.xlsx</x:v>
       </x:c>
       <x:c r="F25" t="str">
         <x:v>id</x:v>
@@ -1486,7 +1486,7 @@
       <x:c r="G25"/>
       <x:c r="H25"/>
       <x:c r="I25" t="str">
-        <x:v>餐桌材质：挂在餐桌碎片格上（TableFragment.materialIds 引用）。effectType/effectValue 定义结算效果。</x:v>
+        <x:v>欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</x:v>
       </x:c>
       <x:c r="J25"/>
       <x:c r="K25"/>
@@ -1494,16 +1494,16 @@
     <x:row r="26">
       <x:c r="A26"/>
       <x:c r="B26" t="str">
-        <x:v>TbCakeLayerBuff</x:v>
+        <x:v>TbSubSkill</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>CakeLayerBuff</x:v>
+        <x:v>SubSkill</x:v>
       </x:c>
       <x:c r="D26" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>cake_layer_buff@dish.xlsx</x:v>
+        <x:v>sub_skill@dish.xlsx</x:v>
       </x:c>
       <x:c r="F26" t="str">
         <x:v>id</x:v>
@@ -1511,7 +1511,7 @@
       <x:c r="G26"/>
       <x:c r="H26"/>
       <x:c r="I26" t="str">
-        <x:v>欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</x:v>
+        <x:v>子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + isPassive/signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</x:v>
       </x:c>
       <x:c r="J26"/>
       <x:c r="K26"/>
@@ -1519,16 +1519,16 @@
     <x:row r="27">
       <x:c r="A27"/>
       <x:c r="B27" t="str">
-        <x:v>TbSubSkill</x:v>
+        <x:v>TbFood</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>SubSkill</x:v>
+        <x:v>Food</x:v>
       </x:c>
       <x:c r="D27" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>sub_skill@dish.xlsx</x:v>
+        <x:v>food@food.xlsx</x:v>
       </x:c>
       <x:c r="F27" t="str">
         <x:v>id</x:v>
@@ -1536,7 +1536,7 @@
       <x:c r="G27"/>
       <x:c r="H27"/>
       <x:c r="I27" t="str">
-        <x:v>子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + isPassive/signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</x:v>
+        <x:v>美食/战斗明细：Food 行动 foodId 关联；actionKind 区分普通/超级/盛宴 Boss。</x:v>
       </x:c>
       <x:c r="J27"/>
       <x:c r="K27"/>
@@ -1544,16 +1544,16 @@
     <x:row r="28">
       <x:c r="A28"/>
       <x:c r="B28" t="str">
-        <x:v>TbFood</x:v>
+        <x:v>TbBossDebuff</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Food</x:v>
+        <x:v>BossDebuff</x:v>
       </x:c>
       <x:c r="D28" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>food@food.xlsx</x:v>
+        <x:v>boss_debuff@food.xlsx</x:v>
       </x:c>
       <x:c r="F28" t="str">
         <x:v>id</x:v>
@@ -1561,7 +1561,7 @@
       <x:c r="G28"/>
       <x:c r="H28"/>
       <x:c r="I28" t="str">
-        <x:v>美食/战斗明细：Food 行动 foodId 关联；actionKind 区分普通/超级/盛宴 Boss。</x:v>
+        <x:v>Boss 盛宴 Debuff：Boss 美食战斗独立抽取，不放回随机；抽空后重置历史。</x:v>
       </x:c>
       <x:c r="J28"/>
       <x:c r="K28"/>
@@ -1569,16 +1569,16 @@
     <x:row r="29">
       <x:c r="A29"/>
       <x:c r="B29" t="str">
-        <x:v>TbBossDebuff</x:v>
+        <x:v>TbEvent</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>BossDebuff</x:v>
+        <x:v>GameEvent</x:v>
       </x:c>
       <x:c r="D29" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>boss_debuff@food.xlsx</x:v>
+        <x:v>event@event.xlsx</x:v>
       </x:c>
       <x:c r="F29" t="str">
         <x:v>id</x:v>
@@ -1586,7 +1586,7 @@
       <x:c r="G29"/>
       <x:c r="H29"/>
       <x:c r="I29" t="str">
-        <x:v>Boss 盛宴 Debuff：Boss 美食战斗独立抽取，不放回随机；抽空后重置历史。</x:v>
+        <x:v>事件明细：eventTypes 用 | 配置多个分类；首项决定权重/保底，全部分类参与对应事件池。公共 preconditions/weight/repeatable。</x:v>
       </x:c>
       <x:c r="J29"/>
       <x:c r="K29"/>
@@ -1594,16 +1594,16 @@
     <x:row r="30">
       <x:c r="A30"/>
       <x:c r="B30" t="str">
-        <x:v>TbEvent</x:v>
+        <x:v>TbEventOption</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>GameEvent</x:v>
+        <x:v>EventOption</x:v>
       </x:c>
       <x:c r="D30" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E30" t="str">
-        <x:v>event@event.xlsx</x:v>
+        <x:v>event_option@event.xlsx</x:v>
       </x:c>
       <x:c r="F30" t="str">
         <x:v>id</x:v>
@@ -1611,7 +1611,7 @@
       <x:c r="G30"/>
       <x:c r="H30"/>
       <x:c r="I30" t="str">
-        <x:v>事件明细：eventTypes 用 | 配置多个分类；首项决定权重/保底，全部分类参与对应事件池。公共 preconditions/weight/repeatable。</x:v>
+        <x:v>事件选项：同 eventId 多行=选项分支；单选项=自动结算。effectType 用 EffectType。</x:v>
       </x:c>
       <x:c r="J30"/>
       <x:c r="K30"/>
@@ -1619,16 +1619,16 @@
     <x:row r="31">
       <x:c r="A31"/>
       <x:c r="B31" t="str">
-        <x:v>TbEventOption</x:v>
+        <x:v>TbActionSmallGroup</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>EventOption</x:v>
+        <x:v>ActionSmallGroup</x:v>
       </x:c>
       <x:c r="D31" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>event_option@event.xlsx</x:v>
+        <x:v>small_group@action.xlsx</x:v>
       </x:c>
       <x:c r="F31" t="str">
         <x:v>id</x:v>
@@ -1636,7 +1636,7 @@
       <x:c r="G31"/>
       <x:c r="H31"/>
       <x:c r="I31" t="str">
-        <x:v>事件选项：同 eventId 多行=选项分支；单选项=自动结算。effectType 用 EffectType。</x:v>
+        <x:v>小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选；weight 供大组挑选。</x:v>
       </x:c>
       <x:c r="J31"/>
       <x:c r="K31"/>
@@ -1644,16 +1644,16 @@
     <x:row r="32">
       <x:c r="A32"/>
       <x:c r="B32" t="str">
-        <x:v>TbActionSmallGroup</x:v>
+        <x:v>TbActionLargeGroup</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>ActionSmallGroup</x:v>
+        <x:v>ActionLargeGroup</x:v>
       </x:c>
       <x:c r="D32" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E32" t="str">
-        <x:v>small_group@action.xlsx</x:v>
+        <x:v>large_group@action.xlsx</x:v>
       </x:c>
       <x:c r="F32" t="str">
         <x:v>id</x:v>
@@ -1661,7 +1661,7 @@
       <x:c r="G32"/>
       <x:c r="H32"/>
       <x:c r="I32" t="str">
-        <x:v>小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选；weight 供大组挑选。</x:v>
+        <x:v>行动大组：内嵌 smallGroupIds(list,string)，按保底上下限与每周权重参与随机。</x:v>
       </x:c>
       <x:c r="J32"/>
       <x:c r="K32"/>
@@ -1669,24 +1669,24 @@
     <x:row r="33">
       <x:c r="A33"/>
       <x:c r="B33" t="str">
-        <x:v>TbActionLargeGroup</x:v>
+        <x:v>TbGameBase</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>ActionLargeGroup</x:v>
+        <x:v>GameBase</x:v>
       </x:c>
       <x:c r="D33" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E33" t="str">
-        <x:v>large_group@action.xlsx</x:v>
-      </x:c>
-      <x:c r="F33" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G33"/>
+        <x:v>game_base.xlsx</x:v>
+      </x:c>
+      <x:c r="F33"/>
+      <x:c r="G33" t="str">
+        <x:v>one</x:v>
+      </x:c>
       <x:c r="H33"/>
       <x:c r="I33" t="str">
-        <x:v>行动大组：内嵌 smallGroupIds(list,string)，按保底权重与日程规则参与随机。</x:v>
+        <x:v>全局基础配置：整局初始金币、利息与商店等基础数值。</x:v>
       </x:c>
       <x:c r="J33"/>
       <x:c r="K33"/>
@@ -1694,50 +1694,38 @@
     <x:row r="34">
       <x:c r="A34"/>
       <x:c r="B34" t="str">
-        <x:v>TbGameBase</x:v>
+        <x:v>TbRecipeGroup</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>GameBase</x:v>
+        <x:v>RecipeGroup</x:v>
       </x:c>
       <x:c r="D34" t="str">
         <x:v>True</x:v>
       </x:c>
       <x:c r="E34" t="str">
-        <x:v>game_base.xlsx</x:v>
-      </x:c>
-      <x:c r="F34"/>
-      <x:c r="G34" t="str">
-        <x:v>one</x:v>
-      </x:c>
+        <x:v>recipe_group@recipe.xlsx</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G34"/>
       <x:c r="H34"/>
       <x:c r="I34" t="str">
-        <x:v>全局基础配置：整局初始金币、利息与商店等基础数值。</x:v>
+        <x:v>菜谱随机小组：仅配置组ID与组内带权放回随机池，菜谱通过 groupIds 正向引用。</x:v>
       </x:c>
       <x:c r="J34"/>
       <x:c r="K34"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35"/>
-      <x:c r="B35" t="str">
-        <x:v>TbRecipeGroup</x:v>
-      </x:c>
-      <x:c r="C35" t="str">
-        <x:v>RecipeGroup</x:v>
-      </x:c>
-      <x:c r="D35" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E35" t="str">
-        <x:v>recipe_group@recipe.xlsx</x:v>
-      </x:c>
-      <x:c r="F35" t="str">
-        <x:v>id</x:v>
-      </x:c>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
       <x:c r="G35"/>
       <x:c r="H35"/>
-      <x:c r="I35" t="str">
-        <x:v>菜谱随机小组：仅配置组ID与组内带权放回随机池，菜谱通过 groupIds 正向引用。</x:v>
-      </x:c>
+      <x:c r="I35"/>
       <x:c r="J35"/>
       <x:c r="K35"/>
     </x:row>
@@ -1782,8 +1770,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Rdfd94f2514e14fbe"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="R17699449759040f5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Rdf393b9b7ff34112"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Rb07d317d71eb4349"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5ce1119519264d92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3bdc25890b448ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -961,7 +961,7 @@
       <x:c r="G4"/>
       <x:c r="H4"/>
       <x:c r="I4" t="str">
-        <x:v>菜品本体：物理属性（id/name/deliciousness/icon/allowRotate/shapeRows）与固有技能（skills→TbSkill）。</x:v>
+        <x:v>食物本体：物理属性（id/name/deliciousness/icon/allowRotate/shapeRows）与固有技能（skills→TbSkill）。</x:v>
       </x:c>
       <x:c r="J4"/>
       <x:c r="K4"/>
@@ -986,7 +986,7 @@
       <x:c r="G5"/>
       <x:c r="H5"/>
       <x:c r="I5" t="str">
-        <x:v>菜品变体：随机菜品库条目。引用本体+风味(flavorId→TbFlavor,单槽)+隐藏分/权重/价格。flavorId 空串=无风味。</x:v>
+        <x:v>食物变体：随机食物库条目。引用本体+风味(flavorId→TbFlavor,单槽)+隐藏分/权重/价格。flavorId 空串=无风味。</x:v>
       </x:c>
       <x:c r="J5"/>
       <x:c r="K5"/>
@@ -1011,7 +1011,7 @@
       <x:c r="G6"/>
       <x:c r="H6"/>
       <x:c r="I6" t="str">
-        <x:v>专有名词：菜品详情右侧框单独解释。</x:v>
+        <x:v>专有名词：食物详情右侧框单独解释。</x:v>
       </x:c>
       <x:c r="J6"/>
       <x:c r="K6"/>
@@ -1036,7 +1036,7 @@
       <x:c r="G7"/>
       <x:c r="H7"/>
       <x:c r="I7" t="str">
-        <x:v>角色：配置初始菜谱/胃形状/道具。</x:v>
+        <x:v>经营方向：配置初始食谱、餐桌形状、装饰品和消耗品。</x:v>
       </x:c>
       <x:c r="J7"/>
       <x:c r="K7"/>
@@ -1061,7 +1061,7 @@
       <x:c r="G8"/>
       <x:c r="H8"/>
       <x:c r="I8" t="str">
-        <x:v>餐桌碎片库：也用作初始餐桌形状来源。materialIds 为该碎片可随机落位的材质列表；碎片不旋转(1x2 与 2x1 视为两个碎片)。'X'=存在格。</x:v>
+        <x:v>餐桌格库：也用作初始餐桌形状来源。materialIds 为该餐桌格可随机落位的材质列表；餐桌格不旋转(1x2 与 2x1 视为两个碎片)。'X'=存在格。</x:v>
       </x:c>
       <x:c r="J8"/>
       <x:c r="K8"/>
@@ -1086,7 +1086,7 @@
       <x:c r="G9"/>
       <x:c r="H9"/>
       <x:c r="I9" t="str">
-        <x:v>菜谱：直接配置有序 groupIds 与带权数量方案 rollPlans；随机小组内容由 TbRecipeGroup 配置。</x:v>
+        <x:v>食谱：直接配置有序 groupIds 与带权数量方案 rollPlans；随机小组内容由 TbRecipeGroup 配置。</x:v>
       </x:c>
       <x:c r="J9"/>
       <x:c r="K9"/>
@@ -1103,7 +1103,7 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="E10" t="str">
-        <x:v>被动道具@item.xlsx</x:v>
+        <x:v>装饰品@item.xlsx</x:v>
       </x:c>
       <x:c r="F10" t="str">
         <x:v>id</x:v>
@@ -1111,7 +1111,7 @@
       <x:c r="G10"/>
       <x:c r="H10"/>
       <x:c r="I10" t="str">
-        <x:v>被动道具：永久常驻/获得时生效，道具池按隐藏分筛选。specialTags 用 | 分隔，空串=无。</x:v>
+        <x:v>装饰品：永久常驻或获得时生效，装饰品池按隐藏分筛选。specialTags 用 | 分隔，空串=无。</x:v>
       </x:c>
       <x:c r="J10"/>
       <x:c r="K10"/>
@@ -1128,7 +1128,7 @@
         <x:v>True</x:v>
       </x:c>
       <x:c r="E11" t="str">
-        <x:v>主动道具@item.xlsx</x:v>
+        <x:v>消耗品@item.xlsx</x:v>
       </x:c>
       <x:c r="F11" t="str">
         <x:v>id</x:v>
@@ -1136,7 +1136,7 @@
       <x:c r="G11"/>
       <x:c r="H11"/>
       <x:c r="I11" t="str">
-        <x:v>主动道具：一次性占全局消耗槽，玩家手动使用；不配置隐藏分区间。specialTags 用 | 分隔，空串=无。</x:v>
+        <x:v>消耗品：一次性占用消耗品栏位，玩家手动使用；不配置隐藏分区间。specialTags 用 | 分隔，空串=无。</x:v>
       </x:c>
       <x:c r="J11"/>
       <x:c r="K11"/>
@@ -1211,7 +1211,7 @@
       <x:c r="G14"/>
       <x:c r="H14"/>
       <x:c r="I14" t="str">
-        <x:v>奖励池筛选：specialTags 用 | 分隔；道具不按品质权重筛选。</x:v>
+        <x:v>奖励池筛选：specialTags 用 | 分隔；装饰品和消耗品不按品质权重筛选。</x:v>
       </x:c>
       <x:c r="J14"/>
       <x:c r="K14"/>
@@ -1236,7 +1236,7 @@
       <x:c r="G15"/>
       <x:c r="H15"/>
       <x:c r="I15" t="str">
-        <x:v>周/关卡配置：定义每周候选行动轴列表与行动轴权重。</x:v>
+        <x:v>周/关卡配置：定义每周候选时间轴列表与时间轴权重。</x:v>
       </x:c>
       <x:c r="J15"/>
       <x:c r="K15"/>
@@ -1286,7 +1286,7 @@
       <x:c r="G17"/>
       <x:c r="H17"/>
       <x:c r="I17" t="str">
-        <x:v>行动轴库：定义行动轴模板与基础长度；具体每周候选池和权重由 Week.timelineIds/timelineWeights 决定。</x:v>
+        <x:v>时间轴库：定义时间轴模板与基础长度；具体每周候选池和权重由 Week.timelineIds/timelineWeights 决定。</x:v>
       </x:c>
       <x:c r="J17"/>
       <x:c r="K17"/>
@@ -1411,7 +1411,7 @@
       <x:c r="G22"/>
       <x:c r="H22"/>
       <x:c r="I22" t="str">
-        <x:v>菜品技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</x:v>
+        <x:v>食物技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</x:v>
       </x:c>
       <x:c r="J22"/>
       <x:c r="K22"/>
@@ -1436,7 +1436,7 @@
       <x:c r="G23"/>
       <x:c r="H23"/>
       <x:c r="I23" t="str">
-        <x:v>菜品风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</x:v>
+        <x:v>食物风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</x:v>
       </x:c>
       <x:c r="J23"/>
       <x:c r="K23"/>
@@ -1461,7 +1461,7 @@
       <x:c r="G24"/>
       <x:c r="H24"/>
       <x:c r="I24" t="str">
-        <x:v>餐桌材质：挂在餐桌碎片格上（TableFragment.materialIds 引用）。effectType/effectValue 定义结算效果。</x:v>
+        <x:v>餐桌材质：挂在餐桌格上（TableFragment.materialIds 引用）。effectType/effectValue 定义结算效果。</x:v>
       </x:c>
       <x:c r="J24"/>
       <x:c r="K24"/>
@@ -1486,7 +1486,7 @@
       <x:c r="G25"/>
       <x:c r="H25"/>
       <x:c r="I25" t="str">
-        <x:v>欢乐蛋糕层数分段buff：结算时读全局层数，layers&gt;=threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</x:v>
+        <x:v>欢乐蛋糕层数分段buff：结算时读全局层数，layers≥threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</x:v>
       </x:c>
       <x:c r="J25"/>
       <x:c r="K25"/>
@@ -1536,7 +1536,7 @@
       <x:c r="G27"/>
       <x:c r="H27"/>
       <x:c r="I27" t="str">
-        <x:v>美食/战斗明细：Food 行动 foodId 关联；actionKind 区分普通/超级/盛宴 Boss。</x:v>
+        <x:v>经营挑战明细：Food 行动 foodId 关联；actionKind 区分日常营业/火热营业/星级评鉴。</x:v>
       </x:c>
       <x:c r="J27"/>
       <x:c r="K27"/>
@@ -1561,7 +1561,7 @@
       <x:c r="G28"/>
       <x:c r="H28"/>
       <x:c r="I28" t="str">
-        <x:v>Boss 盛宴 Debuff：Boss 美食战斗独立抽取，不放回随机；抽空后重置历史。</x:v>
+        <x:v>星级评鉴 Debuff：Boss 经营挑战独立抽取，不放回随机；抽空后重置历史。</x:v>
       </x:c>
       <x:c r="J28"/>
       <x:c r="K28"/>
@@ -1711,7 +1711,7 @@
       <x:c r="G34"/>
       <x:c r="H34"/>
       <x:c r="I34" t="str">
-        <x:v>菜谱随机小组：仅配置组ID与组内带权放回随机池，菜谱通过 groupIds 正向引用。</x:v>
+        <x:v>食谱随机小组：仅配置组ID与组内带权放回随机池，食谱通过 groupIds 正向引用。</x:v>
       </x:c>
       <x:c r="J34"/>
       <x:c r="K34"/>
@@ -1770,8 +1770,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Rdf393b9b7ff34112"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Rb07d317d71eb4349"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Rd8368fac8fc04b16"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Rc0b967218faa4089"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re3bdc25890b448ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R285b33c6a34b47e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="20">
+  <x:fonts count="24">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -123,8 +123,29 @@
       <x:color theme="1"/>
       <x:name val="等线"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color theme="1"/>
+      <x:name val="宋体"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF800080"/>
+      <x:name val="宋体"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="宋体"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="宋体"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="33">
+  <x:fills count="34">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -286,8 +307,13 @@
         <x:fgColor theme="9" tint="0.39998"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7F3F7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="9">
+  <x:borders count="18">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -368,6 +394,96 @@
         <x:color theme="4"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFD8E4E8"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="49">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -518,7 +634,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -527,6 +643,84 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="33" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -845,889 +1039,914 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="30" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="27" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="39" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="88" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" t="str">
+      <x:c r="A1" s="20" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" t="str">
+      <x:c r="B1" s="21" t="str">
         <x:v>full_name</x:v>
       </x:c>
-      <x:c r="C1" t="str">
+      <x:c r="C1" s="21" t="str">
         <x:v>value_type</x:v>
       </x:c>
-      <x:c r="D1" t="str">
+      <x:c r="D1" s="21" t="str">
         <x:v>read_schema_from_file</x:v>
       </x:c>
-      <x:c r="E1" t="str">
+      <x:c r="E1" s="21" t="str">
         <x:v>input</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="F1" s="21" t="str">
         <x:v>index</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="G1" s="21" t="str">
         <x:v>mode</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="H1" s="21" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="I1" s="21" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="J1" t="str">
+      <x:c r="J1" s="21" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="K1" t="str">
+      <x:c r="K1" s="22" t="str">
         <x:v>output</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" t="str">
+      <x:c r="A2" s="23" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B2" t="str">
+      <x:c r="B2" s="24" t="str">
         <x:v>全名(包含模块和名字)</x:v>
       </x:c>
-      <x:c r="C2" t="str">
+      <x:c r="C2" s="24" t="str">
         <x:v>记录类名</x:v>
       </x:c>
-      <x:c r="D2" t="str">
+      <x:c r="D2" s="24" t="str">
         <x:v>从excel读取定义</x:v>
       </x:c>
-      <x:c r="E2" t="str">
+      <x:c r="E2" s="24" t="str">
         <x:v>文件列表</x:v>
       </x:c>
-      <x:c r="F2" t="str">
+      <x:c r="F2" s="24" t="str">
         <x:v>表id字段</x:v>
       </x:c>
-      <x:c r="G2" t="str">
+      <x:c r="G2" s="24" t="str">
         <x:v>模式</x:v>
       </x:c>
-      <x:c r="H2" t="str">
+      <x:c r="H2" s="24" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="I2" t="str">
+      <x:c r="I2" s="24" t="str">
         <x:v>注释</x:v>
       </x:c>
-      <x:c r="J2"/>
-      <x:c r="K2" t="str">
+      <x:c r="J2" s="24"/>
+      <x:c r="K2" s="25" t="str">
         <x:v>输出文件名</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" t="str">
+      <x:c r="A3" s="26" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3"/>
-      <x:c r="C3"/>
-      <x:c r="D3" t="str">
+      <x:c r="B3" s="27"/>
+      <x:c r="C3" s="27"/>
+      <x:c r="D3" s="27" t="str">
         <x:v>false时取已有定义，true为从excel标题头和属性栏读取定义</x:v>
       </x:c>
-      <x:c r="E3" t="str">
+      <x:c r="E3" s="27" t="str">
         <x:v>可以多个，以逗号','分隔</x:v>
       </x:c>
-      <x:c r="F3" t="str">
+      <x:c r="F3" s="27" t="str">
         <x:v>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</x:v>
       </x:c>
-      <x:c r="G3" t="str">
+      <x:c r="G3" s="27" t="str">
         <x:v>取值one|map|list，为空自动为map</x:v>
       </x:c>
-      <x:c r="H3" t="str">
+      <x:c r="H3" s="27" t="str">
         <x:v>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</x:v>
       </x:c>
-      <x:c r="I3"/>
-      <x:c r="J3"/>
-      <x:c r="K3" t="str">
+      <x:c r="I3" s="27"/>
+      <x:c r="J3" s="27"/>
+      <x:c r="K3" s="28" t="str">
         <x:v>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4"/>
-      <x:c r="B4" t="str">
+      <x:c r="A4" s="6"/>
+      <x:c r="B4" s="6" t="str">
         <x:v>TbDishBase</x:v>
       </x:c>
-      <x:c r="C4" t="str">
+      <x:c r="C4" s="6" t="str">
         <x:v>DishBase</x:v>
       </x:c>
-      <x:c r="D4" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E4" t="str">
+      <x:c r="D4" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
         <x:v>dish_base@dish.xlsx</x:v>
       </x:c>
-      <x:c r="F4" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G4"/>
-      <x:c r="H4"/>
-      <x:c r="I4" t="str">
+      <x:c r="F4" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G4" s="6"/>
+      <x:c r="H4" s="6"/>
+      <x:c r="I4" s="6" t="str">
         <x:v>食物本体：物理属性（id/name/deliciousness/icon/allowRotate/shapeRows）与固有技能（skills→TbSkill）。</x:v>
       </x:c>
-      <x:c r="J4"/>
-      <x:c r="K4"/>
+      <x:c r="J4" s="6"/>
+      <x:c r="K4" s="6"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5"/>
-      <x:c r="B5" t="str">
+      <x:c r="A5" s="6"/>
+      <x:c r="B5" s="6" t="str">
         <x:v>TbDishVariant</x:v>
       </x:c>
-      <x:c r="C5" t="str">
+      <x:c r="C5" s="6" t="str">
         <x:v>DishVariant</x:v>
       </x:c>
-      <x:c r="D5" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
+      <x:c r="D5" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
         <x:v>dish_variant@dish.xlsx</x:v>
       </x:c>
-      <x:c r="F5" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G5"/>
-      <x:c r="H5"/>
-      <x:c r="I5" t="str">
+      <x:c r="F5" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G5" s="6"/>
+      <x:c r="H5" s="6"/>
+      <x:c r="I5" s="6" t="str">
         <x:v>食物变体：随机食物库条目。引用本体+风味(flavorId→TbFlavor,单槽)+隐藏分/权重/价格。flavorId 空串=无风味。</x:v>
       </x:c>
-      <x:c r="J5"/>
-      <x:c r="K5"/>
+      <x:c r="J5" s="6"/>
+      <x:c r="K5" s="6"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6"/>
-      <x:c r="B6" t="str">
+      <x:c r="A6" s="6"/>
+      <x:c r="B6" s="6" t="str">
         <x:v>TbTerm</x:v>
       </x:c>
-      <x:c r="C6" t="str">
+      <x:c r="C6" s="6" t="str">
         <x:v>Term</x:v>
       </x:c>
-      <x:c r="D6" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
+      <x:c r="D6" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
         <x:v>term.xlsx</x:v>
       </x:c>
-      <x:c r="F6" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G6"/>
-      <x:c r="H6"/>
-      <x:c r="I6" t="str">
+      <x:c r="F6" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G6" s="6"/>
+      <x:c r="H6" s="6"/>
+      <x:c r="I6" s="6" t="str">
         <x:v>专有名词：食物详情右侧框单独解释。</x:v>
       </x:c>
-      <x:c r="J6"/>
-      <x:c r="K6"/>
+      <x:c r="J6" s="6"/>
+      <x:c r="K6" s="6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7"/>
-      <x:c r="B7" t="str">
+      <x:c r="A7" s="6"/>
+      <x:c r="B7" s="6" t="str">
         <x:v>TbCharacter</x:v>
       </x:c>
-      <x:c r="C7" t="str">
+      <x:c r="C7" s="6" t="str">
         <x:v>Character</x:v>
       </x:c>
-      <x:c r="D7" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
+      <x:c r="D7" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
         <x:v>character.xlsx</x:v>
       </x:c>
-      <x:c r="F7" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G7"/>
-      <x:c r="H7"/>
-      <x:c r="I7" t="str">
+      <x:c r="F7" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G7" s="6"/>
+      <x:c r="H7" s="6"/>
+      <x:c r="I7" s="6" t="str">
         <x:v>经营方向：配置初始食谱、餐桌形状、装饰品和消耗品。</x:v>
       </x:c>
-      <x:c r="J7"/>
-      <x:c r="K7"/>
+      <x:c r="J7" s="6"/>
+      <x:c r="K7" s="6"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8"/>
-      <x:c r="B8" t="str">
+      <x:c r="A8" s="6"/>
+      <x:c r="B8" s="6" t="str">
         <x:v>TbTableFragment</x:v>
       </x:c>
-      <x:c r="C8" t="str">
+      <x:c r="C8" s="6" t="str">
         <x:v>TableFragment</x:v>
       </x:c>
-      <x:c r="D8" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
+      <x:c r="D8" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
         <x:v>table_fragment@fragment_material.xlsx</x:v>
       </x:c>
-      <x:c r="F8" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G8"/>
-      <x:c r="H8"/>
-      <x:c r="I8" t="str">
+      <x:c r="F8" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G8" s="6"/>
+      <x:c r="H8" s="6"/>
+      <x:c r="I8" s="6" t="str">
         <x:v>餐桌格库：也用作初始餐桌形状来源。materialIds 为该餐桌格可随机落位的材质列表；餐桌格不旋转(1x2 与 2x1 视为两个碎片)。'X'=存在格。</x:v>
       </x:c>
-      <x:c r="J8"/>
-      <x:c r="K8"/>
+      <x:c r="J8" s="6"/>
+      <x:c r="K8" s="6"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9"/>
-      <x:c r="B9" t="str">
+      <x:c r="A9" s="6"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>TbRecipe</x:v>
       </x:c>
-      <x:c r="C9" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>Recipe</x:v>
       </x:c>
-      <x:c r="D9" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
+      <x:c r="D9" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
         <x:v>recipe@recipe.xlsx</x:v>
       </x:c>
-      <x:c r="F9" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G9"/>
-      <x:c r="H9"/>
-      <x:c r="I9" t="str">
+      <x:c r="F9" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G9" s="6"/>
+      <x:c r="H9" s="6"/>
+      <x:c r="I9" s="6" t="str">
         <x:v>食谱：直接配置有序 groupIds 与带权数量方案 rollPlans；随机小组内容由 TbRecipeGroup 配置。</x:v>
       </x:c>
-      <x:c r="J9"/>
-      <x:c r="K9"/>
+      <x:c r="J9" s="6"/>
+      <x:c r="K9" s="6"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10"/>
-      <x:c r="B10" t="str">
+      <x:c r="A10" s="6"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>TbPassiveItem</x:v>
       </x:c>
-      <x:c r="C10" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>PassiveItem</x:v>
       </x:c>
-      <x:c r="D10" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
+      <x:c r="D10" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
         <x:v>装饰品@item.xlsx</x:v>
       </x:c>
-      <x:c r="F10" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G10"/>
-      <x:c r="H10"/>
-      <x:c r="I10" t="str">
+      <x:c r="F10" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G10" s="6"/>
+      <x:c r="H10" s="6"/>
+      <x:c r="I10" s="6" t="str">
         <x:v>装饰品：永久常驻或获得时生效，装饰品池按隐藏分筛选。specialTags 用 | 分隔，空串=无。</x:v>
       </x:c>
-      <x:c r="J10"/>
-      <x:c r="K10"/>
+      <x:c r="J10" s="6"/>
+      <x:c r="K10" s="6"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11"/>
-      <x:c r="B11" t="str">
+      <x:c r="A11" s="6"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>TbActiveItem</x:v>
       </x:c>
-      <x:c r="C11" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>ActiveItem</x:v>
       </x:c>
-      <x:c r="D11" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
+      <x:c r="D11" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str">
         <x:v>消耗品@item.xlsx</x:v>
       </x:c>
-      <x:c r="F11" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G11"/>
-      <x:c r="H11"/>
-      <x:c r="I11" t="str">
+      <x:c r="F11" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G11" s="6"/>
+      <x:c r="H11" s="6"/>
+      <x:c r="I11" s="6" t="str">
         <x:v>消耗品：一次性占用消耗品栏位，玩家手动使用；不配置隐藏分区间。specialTags 用 | 分隔，空串=无。</x:v>
       </x:c>
-      <x:c r="J11"/>
-      <x:c r="K11"/>
+      <x:c r="J11" s="6"/>
+      <x:c r="K11" s="6"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12"/>
-      <x:c r="B12" t="str">
+      <x:c r="A12" s="6"/>
+      <x:c r="B12" s="6" t="str">
         <x:v>TbRewardPackage</x:v>
       </x:c>
-      <x:c r="C12" t="str">
+      <x:c r="C12" s="6" t="str">
         <x:v>RewardPackage</x:v>
       </x:c>
-      <x:c r="D12" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
+      <x:c r="D12" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
         <x:v>reward_package@reward.xlsx</x:v>
       </x:c>
-      <x:c r="F12" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G12"/>
-      <x:c r="H12"/>
-      <x:c r="I12" t="str">
+      <x:c r="F12" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G12" s="6"/>
+      <x:c r="H12" s="6"/>
+      <x:c r="I12" s="6" t="str">
         <x:v>奖励包：与奖励槽/奖励池同在 reward.xlsx；Food.rewardPackageId 引用它，槽组指向 reward_slot。</x:v>
       </x:c>
-      <x:c r="J12"/>
-      <x:c r="K12"/>
+      <x:c r="J12" s="6"/>
+      <x:c r="K12" s="6"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13"/>
-      <x:c r="B13" t="str">
+      <x:c r="A13" s="6"/>
+      <x:c r="B13" s="6" t="str">
         <x:v>TbRewardSlot</x:v>
       </x:c>
-      <x:c r="C13" t="str">
+      <x:c r="C13" s="6" t="str">
         <x:v>RewardSlot</x:v>
       </x:c>
-      <x:c r="D13" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E13" t="str">
+      <x:c r="D13" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str">
         <x:v>reward_slot@reward.xlsx</x:v>
       </x:c>
-      <x:c r="F13" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G13"/>
-      <x:c r="H13"/>
-      <x:c r="I13" t="str">
+      <x:c r="F13" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G13" s="6"/>
+      <x:c r="H13" s="6"/>
+      <x:c r="I13" s="6" t="str">
         <x:v>奖励槽：同 groupId 内按 weight 选一个槽，再按槽规则生成候选。</x:v>
       </x:c>
-      <x:c r="J13"/>
-      <x:c r="K13"/>
+      <x:c r="J13" s="6"/>
+      <x:c r="K13" s="6"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14" t="str">
+      <x:c r="A14" s="6"/>
+      <x:c r="B14" s="6" t="str">
         <x:v>TbRewardPool</x:v>
       </x:c>
-      <x:c r="C14" t="str">
+      <x:c r="C14" s="6" t="str">
         <x:v>RewardPool</x:v>
       </x:c>
-      <x:c r="D14" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
+      <x:c r="D14" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str">
         <x:v>reward_pool@reward.xlsx</x:v>
       </x:c>
-      <x:c r="F14" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G14"/>
-      <x:c r="H14"/>
-      <x:c r="I14" t="str">
+      <x:c r="F14" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G14" s="6"/>
+      <x:c r="H14" s="6"/>
+      <x:c r="I14" s="6" t="str">
         <x:v>奖励池筛选：specialTags 用 | 分隔；装饰品和消耗品不按品质权重筛选。</x:v>
       </x:c>
-      <x:c r="J14"/>
-      <x:c r="K14"/>
+      <x:c r="J14" s="6"/>
+      <x:c r="K14" s="6"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15"/>
-      <x:c r="B15" t="str">
+      <x:c r="A15" s="6"/>
+      <x:c r="B15" s="6" t="str">
         <x:v>TbWeek</x:v>
       </x:c>
-      <x:c r="C15" t="str">
+      <x:c r="C15" s="6" t="str">
         <x:v>Week</x:v>
       </x:c>
-      <x:c r="D15" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E15" t="str">
+      <x:c r="D15" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E15" s="6" t="str">
         <x:v>week@timeline.xlsx</x:v>
       </x:c>
-      <x:c r="F15" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G15"/>
-      <x:c r="H15"/>
-      <x:c r="I15" t="str">
+      <x:c r="F15" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G15" s="6"/>
+      <x:c r="H15" s="6"/>
+      <x:c r="I15" s="6" t="str">
         <x:v>周/关卡配置：定义每周候选时间轴列表与时间轴权重。</x:v>
       </x:c>
-      <x:c r="J15"/>
-      <x:c r="K15"/>
+      <x:c r="J15" s="6"/>
+      <x:c r="K15" s="6"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16"/>
-      <x:c r="B16" t="str">
+      <x:c r="A16" s="6"/>
+      <x:c r="B16" s="6" t="str">
         <x:v>TbAction</x:v>
       </x:c>
-      <x:c r="C16" t="str">
+      <x:c r="C16" s="6" t="str">
         <x:v>GameAction</x:v>
       </x:c>
-      <x:c r="D16" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E16" t="str">
+      <x:c r="D16" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E16" s="6" t="str">
         <x:v>action@action.xlsx</x:v>
       </x:c>
-      <x:c r="F16" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G16"/>
-      <x:c r="H16"/>
-      <x:c r="I16" t="str">
+      <x:c r="F16" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G16" s="6"/>
+      <x:c r="H16" s="6"/>
+      <x:c r="I16" s="6" t="str">
         <x:v>行动（薄壳分派）：只留 behavior 与关联/少量参数；具体内容在 TbFood/TbEvent。</x:v>
       </x:c>
-      <x:c r="J16"/>
-      <x:c r="K16"/>
+      <x:c r="J16" s="6"/>
+      <x:c r="K16" s="6"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17"/>
-      <x:c r="B17" t="str">
+      <x:c r="A17" s="6"/>
+      <x:c r="B17" s="6" t="str">
         <x:v>TbTimeline</x:v>
       </x:c>
-      <x:c r="C17" t="str">
+      <x:c r="C17" s="6" t="str">
         <x:v>Timeline</x:v>
       </x:c>
-      <x:c r="D17" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E17" t="str">
+      <x:c r="D17" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E17" s="6" t="str">
         <x:v>timeline@timeline.xlsx</x:v>
       </x:c>
-      <x:c r="F17" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G17"/>
-      <x:c r="H17"/>
-      <x:c r="I17" t="str">
+      <x:c r="F17" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G17" s="6"/>
+      <x:c r="H17" s="6"/>
+      <x:c r="I17" s="6" t="str">
         <x:v>时间轴库：定义时间轴模板与基础长度；具体每周候选池和权重由 Week.timelineIds/timelineWeights 决定。</x:v>
       </x:c>
-      <x:c r="J17"/>
-      <x:c r="K17"/>
+      <x:c r="J17" s="6"/>
+      <x:c r="K17" s="6"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18"/>
-      <x:c r="B18" t="str">
+      <x:c r="A18" s="6"/>
+      <x:c r="B18" s="6" t="str">
         <x:v>TbHiddenScoreCurve</x:v>
       </x:c>
-      <x:c r="C18" t="str">
+      <x:c r="C18" s="6" t="str">
         <x:v>HiddenScoreCurve</x:v>
       </x:c>
-      <x:c r="D18" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E18" t="str">
+      <x:c r="D18" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E18" s="6" t="str">
         <x:v>hidden_score_curve@curve.xlsx</x:v>
       </x:c>
-      <x:c r="F18" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G18"/>
-      <x:c r="H18"/>
-      <x:c r="I18" t="str">
+      <x:c r="F18" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G18" s="6"/>
+      <x:c r="H18" s="6"/>
+      <x:c r="I18" s="6" t="str">
         <x:v>隐藏分曲线：基础隐藏分与派生隐藏分。</x:v>
       </x:c>
-      <x:c r="J18"/>
-      <x:c r="K18"/>
+      <x:c r="J18" s="6"/>
+      <x:c r="K18" s="6"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19"/>
-      <x:c r="B19" t="str">
+      <x:c r="A19" s="6"/>
+      <x:c r="B19" s="6" t="str">
         <x:v>TbGoldRewardCurve</x:v>
       </x:c>
-      <x:c r="C19" t="str">
+      <x:c r="C19" s="6" t="str">
         <x:v>GoldRewardCurve</x:v>
       </x:c>
-      <x:c r="D19" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E19" t="str">
+      <x:c r="D19" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="str">
         <x:v>gold_reward_curve@curve.xlsx</x:v>
       </x:c>
-      <x:c r="F19" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
-      <x:c r="I19" t="str">
+      <x:c r="F19" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G19" s="6"/>
+      <x:c r="H19" s="6"/>
+      <x:c r="I19" s="6" t="str">
         <x:v>金币奖励曲线：按进度计算中心值，并按 fluctuationPct 浮动取值。</x:v>
       </x:c>
-      <x:c r="J19"/>
-      <x:c r="K19"/>
+      <x:c r="J19" s="6"/>
+      <x:c r="K19" s="6"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20"/>
-      <x:c r="B20" t="str">
+      <x:c r="A20" s="6"/>
+      <x:c r="B20" s="6" t="str">
         <x:v>TbUnlockRule</x:v>
       </x:c>
-      <x:c r="C20" t="str">
+      <x:c r="C20" s="6" t="str">
         <x:v>UnlockRule</x:v>
       </x:c>
-      <x:c r="D20" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="str">
+      <x:c r="D20" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E20" s="7" t="str">
         <x:v>unlock_rule@unlock.xlsx</x:v>
       </x:c>
-      <x:c r="F20" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G20"/>
-      <x:c r="H20"/>
-      <x:c r="I20" t="str">
+      <x:c r="F20" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G20" s="6"/>
+      <x:c r="H20" s="6"/>
+      <x:c r="I20" s="6" t="str">
         <x:v>解锁规则：一条规则定义一个跨局可解锁目标。</x:v>
       </x:c>
-      <x:c r="J20"/>
-      <x:c r="K20"/>
+      <x:c r="J20" s="6"/>
+      <x:c r="K20" s="6"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21"/>
-      <x:c r="B21" t="str">
+      <x:c r="A21" s="6"/>
+      <x:c r="B21" s="6" t="str">
         <x:v>TbUnlockCondition</x:v>
       </x:c>
-      <x:c r="C21" t="str">
+      <x:c r="C21" s="6" t="str">
         <x:v>UnlockCondition</x:v>
       </x:c>
-      <x:c r="D21" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E21" s="2" t="str">
+      <x:c r="D21" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E21" s="8" t="str">
         <x:v>unlock_condition@unlock.xlsx</x:v>
       </x:c>
-      <x:c r="F21" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G21"/>
-      <x:c r="H21"/>
-      <x:c r="I21" t="str">
+      <x:c r="F21" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G21" s="6"/>
+      <x:c r="H21" s="6"/>
+      <x:c r="I21" s="6" t="str">
         <x:v>解锁条件：同 ruleId 的条件按 groupId 组成 OR-of-AND。</x:v>
       </x:c>
-      <x:c r="J21"/>
-      <x:c r="K21"/>
+      <x:c r="J21" s="6"/>
+      <x:c r="K21" s="6"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22"/>
-      <x:c r="B22" t="str">
+      <x:c r="A22" s="6"/>
+      <x:c r="B22" s="6" t="str">
         <x:v>TbSkill</x:v>
       </x:c>
-      <x:c r="C22" t="str">
+      <x:c r="C22" s="6" t="str">
         <x:v>Skill</x:v>
       </x:c>
-      <x:c r="D22" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
+      <x:c r="D22" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E22" s="6" t="str">
         <x:v>skill@dish.xlsx</x:v>
       </x:c>
-      <x:c r="F22" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G22"/>
-      <x:c r="H22"/>
-      <x:c r="I22" t="str">
+      <x:c r="F22" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G22" s="6"/>
+      <x:c r="H22" s="6"/>
+      <x:c r="I22" s="6" t="str">
         <x:v>食物技能元信息：id/termId/descOverride/subSkills(有序引用 sub_skill)。描述由所含子技能占位符模板按顺序自动拼接；descOverride 非空时覆盖。表标题按 termId 术语名(无则空)。</x:v>
       </x:c>
-      <x:c r="J22"/>
-      <x:c r="K22"/>
+      <x:c r="J22" s="6"/>
+      <x:c r="K22" s="6"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23"/>
-      <x:c r="B23" t="str">
+      <x:c r="A23" s="6"/>
+      <x:c r="B23" s="6" t="str">
         <x:v>TbFlavor</x:v>
       </x:c>
-      <x:c r="C23" t="str">
+      <x:c r="C23" s="6" t="str">
         <x:v>Flavor</x:v>
       </x:c>
-      <x:c r="D23" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E23" t="str">
+      <x:c r="D23" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E23" s="6" t="str">
         <x:v>flavor@dish.xlsx</x:v>
       </x:c>
-      <x:c r="F23" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G23"/>
-      <x:c r="H23"/>
-      <x:c r="I23" t="str">
+      <x:c r="F23" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G23" s="6"/>
+      <x:c r="H23" s="6"/>
+      <x:c r="I23" s="6" t="str">
         <x:v>食物风味：单槽，后者替换前者。effectType/effectValue 定义简易结算效果。</x:v>
       </x:c>
-      <x:c r="J23"/>
-      <x:c r="K23"/>
+      <x:c r="J23" s="6"/>
+      <x:c r="K23" s="6"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24"/>
-      <x:c r="B24" t="str">
+      <x:c r="A24" s="6"/>
+      <x:c r="B24" s="6" t="str">
         <x:v>TbMaterial</x:v>
       </x:c>
-      <x:c r="C24" t="str">
+      <x:c r="C24" s="6" t="str">
         <x:v>Material</x:v>
       </x:c>
-      <x:c r="D24" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E24" t="str">
+      <x:c r="D24" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="str">
         <x:v>material@fragment_material.xlsx</x:v>
       </x:c>
-      <x:c r="F24" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G24"/>
-      <x:c r="H24"/>
-      <x:c r="I24" t="str">
+      <x:c r="F24" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G24" s="6"/>
+      <x:c r="H24" s="6"/>
+      <x:c r="I24" s="6" t="str">
         <x:v>餐桌材质：挂在餐桌格上（TableFragment.materialIds 引用）。effectType/effectValue 定义结算效果。</x:v>
       </x:c>
-      <x:c r="J24"/>
-      <x:c r="K24"/>
+      <x:c r="J24" s="6"/>
+      <x:c r="K24" s="6"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25"/>
-      <x:c r="B25" t="str">
+      <x:c r="A25" s="6"/>
+      <x:c r="B25" s="6" t="str">
         <x:v>TbCakeLayerBuff</x:v>
       </x:c>
-      <x:c r="C25" t="str">
+      <x:c r="C25" s="6" t="str">
         <x:v>CakeLayerBuff</x:v>
       </x:c>
-      <x:c r="D25" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E25" t="str">
+      <x:c r="D25" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E25" s="6" t="str">
         <x:v>cake_layer_buff@dish.xlsx</x:v>
       </x:c>
-      <x:c r="F25" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G25"/>
-      <x:c r="H25"/>
-      <x:c r="I25" t="str">
+      <x:c r="F25" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G25" s="6"/>
+      <x:c r="H25" s="6"/>
+      <x:c r="I25" s="6" t="str">
         <x:v>欢乐蛋糕层数分段buff：结算时读全局层数，layers≥threshold 的档累计应用到 category 分类所有食物。effectType 复用 SkillActionType。</x:v>
       </x:c>
-      <x:c r="J25"/>
-      <x:c r="K25"/>
+      <x:c r="J25" s="6"/>
+      <x:c r="K25" s="6"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26"/>
-      <x:c r="B26" t="str">
+      <x:c r="A26" s="6"/>
+      <x:c r="B26" s="6" t="str">
         <x:v>TbSubSkill</x:v>
       </x:c>
-      <x:c r="C26" t="str">
+      <x:c r="C26" s="6" t="str">
         <x:v>SubSkill</x:v>
       </x:c>
-      <x:c r="D26" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E26" t="str">
+      <x:c r="D26" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E26" s="6" t="str">
         <x:v>sub_skill@dish.xlsx</x:v>
       </x:c>
-      <x:c r="F26" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G26"/>
-      <x:c r="H26"/>
-      <x:c r="I26" t="str">
+      <x:c r="F26" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G26" s="6"/>
+      <x:c r="H26" s="6"/>
+      <x:c r="I26" s="6" t="str">
         <x:v>子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + isPassive/signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</x:v>
       </x:c>
-      <x:c r="J26"/>
-      <x:c r="K26"/>
+      <x:c r="J26" s="6"/>
+      <x:c r="K26" s="6"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27"/>
-      <x:c r="B27" t="str">
+      <x:c r="A27" s="6"/>
+      <x:c r="B27" s="6" t="str">
         <x:v>TbFood</x:v>
       </x:c>
-      <x:c r="C27" t="str">
+      <x:c r="C27" s="6" t="str">
         <x:v>Food</x:v>
       </x:c>
-      <x:c r="D27" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E27" t="str">
+      <x:c r="D27" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E27" s="6" t="str">
         <x:v>food@food.xlsx</x:v>
       </x:c>
-      <x:c r="F27" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G27"/>
-      <x:c r="H27"/>
-      <x:c r="I27" t="str">
+      <x:c r="F27" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G27" s="6"/>
+      <x:c r="H27" s="6"/>
+      <x:c r="I27" s="6" t="str">
         <x:v>经营挑战明细：Food 行动 foodId 关联；actionKind 区分日常营业/火热营业/星级评鉴。</x:v>
       </x:c>
-      <x:c r="J27"/>
-      <x:c r="K27"/>
+      <x:c r="J27" s="6"/>
+      <x:c r="K27" s="6"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28"/>
-      <x:c r="B28" t="str">
+      <x:c r="A28" s="6"/>
+      <x:c r="B28" s="6" t="str">
         <x:v>TbBossDebuff</x:v>
       </x:c>
-      <x:c r="C28" t="str">
+      <x:c r="C28" s="6" t="str">
         <x:v>BossDebuff</x:v>
       </x:c>
-      <x:c r="D28" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E28" t="str">
+      <x:c r="D28" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E28" s="6" t="str">
         <x:v>boss_debuff@food.xlsx</x:v>
       </x:c>
-      <x:c r="F28" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G28"/>
-      <x:c r="H28"/>
-      <x:c r="I28" t="str">
+      <x:c r="F28" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G28" s="6"/>
+      <x:c r="H28" s="6"/>
+      <x:c r="I28" s="6" t="str">
         <x:v>星级评鉴 Debuff：Boss 经营挑战独立抽取，不放回随机；抽空后重置历史。</x:v>
       </x:c>
-      <x:c r="J28"/>
-      <x:c r="K28"/>
+      <x:c r="J28" s="6"/>
+      <x:c r="K28" s="6"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29"/>
-      <x:c r="B29" t="str">
+      <x:c r="A29" s="6"/>
+      <x:c r="B29" s="6" t="str">
         <x:v>TbEvent</x:v>
       </x:c>
-      <x:c r="C29" t="str">
+      <x:c r="C29" s="6" t="str">
         <x:v>GameEvent</x:v>
       </x:c>
-      <x:c r="D29" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E29" t="str">
+      <x:c r="D29" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E29" s="6" t="str">
         <x:v>event@event.xlsx</x:v>
       </x:c>
-      <x:c r="F29" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G29"/>
-      <x:c r="H29"/>
-      <x:c r="I29" t="str">
+      <x:c r="F29" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G29" s="6"/>
+      <x:c r="H29" s="6"/>
+      <x:c r="I29" s="6" t="str">
         <x:v>事件明细：eventTypes 用 | 配置多个分类；首项决定权重/保底，全部分类参与对应事件池。公共 preconditions/weight/repeatable。</x:v>
       </x:c>
-      <x:c r="J29"/>
-      <x:c r="K29"/>
+      <x:c r="J29" s="6"/>
+      <x:c r="K29" s="6"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30"/>
-      <x:c r="B30" t="str">
+      <x:c r="A30" s="6"/>
+      <x:c r="B30" s="6" t="str">
         <x:v>TbEventOption</x:v>
       </x:c>
-      <x:c r="C30" t="str">
+      <x:c r="C30" s="6" t="str">
         <x:v>EventOption</x:v>
       </x:c>
-      <x:c r="D30" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E30" t="str">
+      <x:c r="D30" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E30" s="6" t="str">
         <x:v>event_option@event.xlsx</x:v>
       </x:c>
-      <x:c r="F30" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G30"/>
-      <x:c r="H30"/>
-      <x:c r="I30" t="str">
+      <x:c r="F30" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G30" s="6"/>
+      <x:c r="H30" s="6"/>
+      <x:c r="I30" s="6" t="str">
         <x:v>事件选项：同 eventId 多行=选项分支；单选项=自动结算。effectType 用 EffectType。</x:v>
       </x:c>
-      <x:c r="J30"/>
-      <x:c r="K30"/>
+      <x:c r="J30" s="6"/>
+      <x:c r="K30" s="6"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31"/>
-      <x:c r="B31" t="str">
-        <x:v>TbActionSmallGroup</x:v>
-      </x:c>
-      <x:c r="C31" t="str">
-        <x:v>ActionSmallGroup</x:v>
-      </x:c>
-      <x:c r="D31" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E31" t="str">
-        <x:v>small_group@action.xlsx</x:v>
-      </x:c>
-      <x:c r="F31" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G31"/>
-      <x:c r="H31"/>
-      <x:c r="I31" t="str">
-        <x:v>小组：内嵌 actionIds(list,string)，固定成员即本次 n 选一候选；weight 供大组挑选。</x:v>
-      </x:c>
-      <x:c r="J31"/>
-      <x:c r="K31"/>
+      <x:c r="A31" s="6"/>
+      <x:c r="B31" s="6" t="str">
+        <x:v>TbActionChoiceCountRule</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="str">
+        <x:v>ActionChoiceCountRule</x:v>
+      </x:c>
+      <x:c r="D31" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E31" s="6" t="str">
+        <x:v>choice_count_rule@action.xlsx</x:v>
+      </x:c>
+      <x:c r="F31" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G31" s="6"/>
+      <x:c r="H31" s="6"/>
+      <x:c r="I31" s="6" t="str">
+        <x:v>日常行动候选数洗牌袋规则：每周整数票数。</x:v>
+      </x:c>
+      <x:c r="J31" s="6"/>
+      <x:c r="K31" s="6"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32"/>
-      <x:c r="B32" t="str">
-        <x:v>TbActionLargeGroup</x:v>
-      </x:c>
-      <x:c r="C32" t="str">
-        <x:v>ActionLargeGroup</x:v>
-      </x:c>
-      <x:c r="D32" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E32" t="str">
-        <x:v>large_group@action.xlsx</x:v>
-      </x:c>
-      <x:c r="F32" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G32"/>
-      <x:c r="H32"/>
-      <x:c r="I32" t="str">
-        <x:v>行动大组：内嵌 smallGroupIds(list,string)，按保底上下限与每周权重参与随机。</x:v>
-      </x:c>
-      <x:c r="J32"/>
-      <x:c r="K32"/>
+      <x:c r="A32" s="6"/>
+      <x:c r="B32" s="6" t="str">
+        <x:v>TbActionCategoryRule</x:v>
+      </x:c>
+      <x:c r="C32" s="6" t="str">
+        <x:v>ActionCategoryRule</x:v>
+      </x:c>
+      <x:c r="D32" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E32" s="6" t="str">
+        <x:v>category_rule@action.xlsx</x:v>
+      </x:c>
+      <x:c r="F32" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G32" s="6"/>
+      <x:c r="H32" s="6"/>
+      <x:c r="I32" s="6" t="str">
+        <x:v>日常行动类别规则：每周权重与逐候选卡累计上下保底。</x:v>
+      </x:c>
+      <x:c r="J32" s="6"/>
+      <x:c r="K32" s="6"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33"/>
-      <x:c r="B33" t="str">
+      <x:c r="A33" s="6"/>
+      <x:c r="B33" s="6" t="str">
+        <x:v>TbActionRewardRule</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="str">
+        <x:v>ActionRewardRule</x:v>
+      </x:c>
+      <x:c r="D33" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E33" s="6" t="str">
+        <x:v>reward_rule@action.xlsx</x:v>
+      </x:c>
+      <x:c r="F33" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G33" s="6"/>
+      <x:c r="H33" s="6"/>
+      <x:c r="I33" s="6" t="str">
+        <x:v>日常行动奖励规则：复用 RewardKind，配置每周权重与逐候选卡累计上下保底。</x:v>
+      </x:c>
+      <x:c r="J33" s="6"/>
+      <x:c r="K33" s="6"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="6"/>
+      <x:c r="B34" s="6" t="str">
         <x:v>TbGameBase</x:v>
       </x:c>
-      <x:c r="C33" t="str">
+      <x:c r="C34" s="6" t="str">
         <x:v>GameBase</x:v>
       </x:c>
-      <x:c r="D33" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E33" t="str">
+      <x:c r="D34" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E34" s="6" t="str">
         <x:v>game_base.xlsx</x:v>
       </x:c>
-      <x:c r="F33"/>
-      <x:c r="G33" t="str">
+      <x:c r="F34" s="6"/>
+      <x:c r="G34" s="6" t="str">
         <x:v>one</x:v>
       </x:c>
-      <x:c r="H33"/>
-      <x:c r="I33" t="str">
+      <x:c r="H34" s="6"/>
+      <x:c r="I34" s="6" t="str">
         <x:v>全局基础配置：整局初始金币、利息与商店等基础数值。</x:v>
       </x:c>
-      <x:c r="J33"/>
-      <x:c r="K33"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34"/>
-      <x:c r="B34" t="str">
+      <x:c r="J34" s="6"/>
+      <x:c r="K34" s="6"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="6"/>
+      <x:c r="B35" s="6" t="str">
         <x:v>TbRecipeGroup</x:v>
       </x:c>
-      <x:c r="C34" t="str">
+      <x:c r="C35" s="6" t="str">
         <x:v>RecipeGroup</x:v>
       </x:c>
-      <x:c r="D34" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="E34" t="str">
+      <x:c r="D35" s="6" t="str">
+        <x:v>True</x:v>
+      </x:c>
+      <x:c r="E35" s="6" t="str">
         <x:v>recipe_group@recipe.xlsx</x:v>
       </x:c>
-      <x:c r="F34" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="G34"/>
-      <x:c r="H34"/>
-      <x:c r="I34" t="str">
+      <x:c r="F35" s="6" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="G35" s="6"/>
+      <x:c r="H35" s="6"/>
+      <x:c r="I35" s="6" t="str">
         <x:v>食谱随机小组：仅配置组ID与组内带权放回随机池，食谱通过 groupIds 正向引用。</x:v>
       </x:c>
-      <x:c r="J34"/>
-      <x:c r="K34"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35"/>
-      <x:c r="B35"/>
-      <x:c r="C35"/>
-      <x:c r="D35"/>
-      <x:c r="E35"/>
-      <x:c r="F35"/>
-      <x:c r="G35"/>
-      <x:c r="H35"/>
-      <x:c r="I35"/>
-      <x:c r="J35"/>
-      <x:c r="K35"/>
+      <x:c r="J35" s="6"/>
+      <x:c r="K35" s="6"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36"/>
@@ -1770,8 +1989,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Rd8368fac8fc04b16"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Rc0b967218faa4089"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="R08152fe3612f4de1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Rd8c811685bae406a"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GourmetProject/GameConfig/Datas/__tables__.xlsx
+++ b/GourmetProject/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R285b33c6a34b47e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc827d4bd8f74457"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1718,7 +1718,7 @@
       <x:c r="G26" s="6"/>
       <x:c r="H26" s="6"/>
       <x:c r="I26" s="6" t="str">
-        <x:v>子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + isPassive/signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</x:v>
+        <x:v>子技能(合并后=具体子技能)：一行=一条完整效果(全部 SkillRuleDef 字段 + signed/descTemplate)。参数不同即不同子技能，内容相同可被多个技能复用。</x:v>
       </x:c>
       <x:c r="J26" s="6"/>
       <x:c r="K26" s="6"/>
@@ -1989,8 +1989,8 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="R08152fe3612f4de1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="Rd8c811685bae406a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="Rb3cc9f29c96a40dc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="R0963a9fbb3ee4df4"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
